--- a/2026/YRIGOYEN 7630/Junio/YRIGOYEN7630-Junio.xlsx
+++ b/2026/YRIGOYEN 7630/Junio/YRIGOYEN7630-Junio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34608F0-547F-414D-B53F-538ADC601BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEDAD97-B4A7-4D84-9AFE-86A819CC9663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$115</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$119</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="130">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -338,45 +338,15 @@
     <t>Ivan Gstavo Almeyda</t>
   </si>
   <si>
-    <t>VTO 18/06</t>
-  </si>
-  <si>
-    <t>PERÍODO: MAYO</t>
-  </si>
-  <si>
-    <t>Gustavo padron - Sr contador honorarios MAYO</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de MAYO</t>
-  </si>
-  <si>
     <t>Transf 22/05</t>
   </si>
   <si>
-    <t>Transf 21/05</t>
-  </si>
-  <si>
-    <t>Transf 08/05</t>
-  </si>
-  <si>
-    <t>Julio Doartero - Cambio de cañeria interna de desague, descarga de bañera, descarga de vanitory y descarga de videt, mano de obra y materiales</t>
-  </si>
-  <si>
-    <t>Trans 12/05</t>
-  </si>
-  <si>
-    <t>Transf 05/05</t>
-  </si>
-  <si>
     <t>Debito 11/05</t>
   </si>
   <si>
     <t>Debito 18/05</t>
   </si>
   <si>
-    <t>Honorarios administracion - Abril y Mayo</t>
-  </si>
-  <si>
     <t>Subidos en Juni0 a 165000</t>
   </si>
   <si>
@@ -402,6 +372,51 @@
   </si>
   <si>
     <t>El mes pasado abono los $5.028 que le habian quedado como deuda y se nos paso</t>
+  </si>
+  <si>
+    <t>VTO 17/07</t>
+  </si>
+  <si>
+    <t>PERÍODO: JUNIO</t>
+  </si>
+  <si>
+    <t>Gustavo padron - Sr contador honorarios JUNIO</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de JUNIO</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - MAYO y JUNIO</t>
+  </si>
+  <si>
+    <t>Transf 24/06</t>
+  </si>
+  <si>
+    <t>Transf 05/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kromacolor </t>
+  </si>
+  <si>
+    <t>Transf 13/06</t>
+  </si>
+  <si>
+    <t>Transf 16/06</t>
+  </si>
+  <si>
+    <t>Doartero Julio - Colocacion de tres sombreros para ventilacion . 2 caños para ventilacion. Reparacion de perdida de agua en cañeria de motor. Mano de obra y materiales</t>
+  </si>
+  <si>
+    <t>Matafuegos FIRE - Uniforme encargado</t>
+  </si>
+  <si>
+    <t>Efectivo</t>
+  </si>
+  <si>
+    <t>Envio carta documento PB2 - Sra. Roxana Goldemberg</t>
+  </si>
+  <si>
+    <t>Envio Carta documento - Correo Argentino</t>
   </si>
 </sst>
 </file>
@@ -1106,7 +1121,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="233">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1376,104 +1391,110 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1838,7 +1859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M119"/>
+  <dimension ref="A1:M123"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.5546875" customWidth="1"/>
@@ -1873,12 +1894,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16"/>
-      <c r="B3" s="195" t="s">
+      <c r="B3" s="204" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="195"/>
-      <c r="D3" s="195"/>
-      <c r="E3" s="196"/>
+      <c r="C3" s="204"/>
+      <c r="D3" s="204"/>
+      <c r="E3" s="205"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
@@ -1896,7 +1917,7 @@
         <v>55</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="71" t="s">
@@ -1916,49 +1937,49 @@
       <c r="E6" s="21"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="198" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="198"/>
+      <c r="B8" s="207" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="207"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="198"/>
-      <c r="C9" s="198"/>
+      <c r="B9" s="207"/>
+      <c r="C9" s="207"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="198"/>
-      <c r="C10" s="198"/>
+      <c r="B10" s="207"/>
+      <c r="C10" s="207"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="197" t="s">
+      <c r="A13" s="206" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="197"/>
-      <c r="C13" s="197"/>
-      <c r="D13" s="197"/>
-      <c r="E13" s="197"/>
+      <c r="B13" s="206"/>
+      <c r="C13" s="206"/>
+      <c r="D13" s="206"/>
+      <c r="E13" s="206"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="197"/>
-      <c r="B14" s="197"/>
-      <c r="C14" s="197"/>
-      <c r="D14" s="197"/>
-      <c r="E14" s="197"/>
+      <c r="A14" s="206"/>
+      <c r="B14" s="206"/>
+      <c r="C14" s="206"/>
+      <c r="D14" s="206"/>
+      <c r="E14" s="206"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="197"/>
-      <c r="B15" s="197"/>
-      <c r="C15" s="197"/>
-      <c r="D15" s="197"/>
-      <c r="E15" s="197"/>
+      <c r="A15" s="206"/>
+      <c r="B15" s="206"/>
+      <c r="C15" s="206"/>
+      <c r="D15" s="206"/>
+      <c r="E15" s="206"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="197"/>
-      <c r="B16" s="197"/>
-      <c r="C16" s="197"/>
-      <c r="D16" s="197"/>
-      <c r="E16" s="197"/>
+      <c r="A16" s="206"/>
+      <c r="B16" s="206"/>
+      <c r="C16" s="206"/>
+      <c r="D16" s="206"/>
+      <c r="E16" s="206"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
@@ -1990,7 +2011,7 @@
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="169">
-        <v>972126</v>
+        <v>1561247</v>
       </c>
       <c r="E22" s="5"/>
     </row>
@@ -2009,7 +2030,7 @@
       <c r="C24" s="57"/>
       <c r="D24" s="170">
         <f>SUM(D22:D23)</f>
-        <v>972126</v>
+        <v>1561247</v>
       </c>
       <c r="E24" s="139"/>
       <c r="G24" s="22"/>
@@ -2075,7 +2096,7 @@
       <c r="D30" s="173"/>
       <c r="E30" s="140">
         <f>D24+D29</f>
-        <v>972126</v>
+        <v>1561247</v>
       </c>
       <c r="F30" s="22"/>
     </row>
@@ -2089,21 +2110,21 @@
       <c r="E31" s="141"/>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="193" t="s">
-        <v>105</v>
-      </c>
-      <c r="B32" s="194"/>
+      <c r="A32" s="202" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="203"/>
       <c r="C32" s="52"/>
-      <c r="D32" s="169">
+      <c r="D32" s="231">
         <v>45000</v>
       </c>
       <c r="E32" s="142"/>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="193" t="s">
-        <v>115</v>
-      </c>
-      <c r="B33" s="194"/>
+      <c r="A33" s="202" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" s="203"/>
       <c r="C33" s="52"/>
       <c r="D33" s="175">
         <f>147300*2</f>
@@ -2111,7 +2132,7 @@
       </c>
       <c r="E33" s="142"/>
       <c r="H33" s="152" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2136,24 +2157,24 @@
       <c r="E35" s="144"/>
     </row>
     <row r="36" spans="1:8" s="38" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="199" t="s">
+      <c r="A36" s="200" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="200"/>
+      <c r="B36" s="201"/>
       <c r="C36" s="54"/>
       <c r="D36" s="178">
         <f>26570+7909</f>
         <v>34479</v>
       </c>
       <c r="E36" s="163" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="193" t="s">
+      <c r="A37" s="202" t="s">
         <v>89</v>
       </c>
-      <c r="B37" s="194"/>
+      <c r="B37" s="203"/>
       <c r="C37" s="54"/>
       <c r="D37" s="179">
         <v>54278</v>
@@ -2190,11 +2211,11 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="52"/>
-      <c r="D40" s="181">
-        <v>681424.8</v>
+      <c r="D40" s="230">
+        <v>707699.22</v>
       </c>
       <c r="E40" s="163" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="G40" s="124"/>
     </row>
@@ -2208,7 +2229,7 @@
         <v>10602.27</v>
       </c>
       <c r="E41" s="154" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
@@ -2232,11 +2253,11 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
-      <c r="D43" s="157">
+      <c r="D43" s="229">
         <v>102476.36</v>
       </c>
       <c r="E43" s="154" t="str">
@@ -2247,12 +2268,12 @@
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="str">
         <f>A43</f>
-        <v>Sindicatos mes de MAYO</v>
+        <v>Sindicatos mes de JUNIO</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
-      <c r="D44" s="157">
-        <v>6219.95</v>
+      <c r="D44" s="229">
+        <v>106451.98</v>
       </c>
       <c r="E44" s="155" t="str">
         <f>E43</f>
@@ -2262,12 +2283,12 @@
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="str">
         <f>A44</f>
-        <v>Sindicatos mes de MAYO</v>
+        <v>Sindicatos mes de JUNIO</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
-      <c r="D45" s="157">
-        <v>55979.55</v>
+      <c r="D45" s="229">
+        <v>58133.75</v>
       </c>
       <c r="E45" s="156" t="str">
         <f>E44</f>
@@ -2283,7 +2304,7 @@
       <c r="D46" s="182"/>
       <c r="E46" s="146">
         <f>SUM(D40:D45)</f>
-        <v>932235.22000000009</v>
+        <v>1060895.8700000001</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
@@ -2301,11 +2322,11 @@
       </c>
       <c r="B48" s="157"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="157">
-        <v>82654.19</v>
-      </c>
-      <c r="E48" s="154" t="s">
-        <v>109</v>
+      <c r="D48" s="229">
+        <v>69293.56</v>
+      </c>
+      <c r="E48" s="158" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2314,12 +2335,11 @@
       </c>
       <c r="B49" s="157"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="157">
-        <v>35559.360000000001</v>
-      </c>
-      <c r="E49" s="154" t="str">
-        <f>E48</f>
-        <v>Transf 08/05</v>
+      <c r="D49" s="229">
+        <v>29349.599999999999</v>
+      </c>
+      <c r="E49" s="158" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -2331,22 +2351,21 @@
       <c r="D50" s="157">
         <v>29818.65</v>
       </c>
-      <c r="E50" s="154" t="str">
-        <f>E49</f>
-        <v>Transf 08/05</v>
+      <c r="E50" s="158" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="199" t="s">
+      <c r="A51" s="200" t="s">
         <v>75</v>
       </c>
-      <c r="B51" s="200"/>
+      <c r="B51" s="201"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="157">
-        <v>838862.61</v>
-      </c>
-      <c r="E51" s="154" t="s">
-        <v>112</v>
+      <c r="D51" s="229">
+        <v>837249.05</v>
+      </c>
+      <c r="E51" s="158" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2358,7 +2377,7 @@
       <c r="D52" s="183"/>
       <c r="E52" s="146">
         <f>SUM(D48:D51)</f>
-        <v>986894.81</v>
+        <v>965710.8600000001</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2376,11 +2395,11 @@
       </c>
       <c r="B54" s="153"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="157">
+      <c r="D54" s="229">
         <v>93200</v>
       </c>
       <c r="E54" s="158" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -2393,519 +2412,562 @@
         <v>55000</v>
       </c>
       <c r="E55" s="158" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="199" t="s">
-        <v>117</v>
-      </c>
-      <c r="B56" s="200"/>
+      <c r="A56" s="200" t="s">
+        <v>107</v>
+      </c>
+      <c r="B56" s="201"/>
       <c r="C56" s="5"/>
       <c r="D56" s="106">
         <v>333100</v>
       </c>
       <c r="E56" s="158" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="199" t="s">
-        <v>110</v>
-      </c>
-      <c r="B57" s="200"/>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="105" t="s">
+        <v>122</v>
+      </c>
+      <c r="B57" s="153"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="106">
-        <v>250000</v>
+      <c r="D57" s="128">
+        <v>334393.40999999997</v>
       </c>
       <c r="E57" s="158" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="199" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="200" t="s">
+        <v>125</v>
+      </c>
+      <c r="B58" s="201"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="128">
+        <v>235000</v>
+      </c>
+      <c r="E58" s="158" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="200" t="s">
+        <v>126</v>
+      </c>
+      <c r="B59" s="201"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="128">
+        <v>127640</v>
+      </c>
+      <c r="E59" s="158" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="200" t="s">
         <v>93</v>
       </c>
-      <c r="B58" s="200"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="106">
-        <v>78200</v>
-      </c>
-      <c r="E58" s="158" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="29" t="s">
+      <c r="B60" s="201"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="128">
+        <v>103100</v>
+      </c>
+      <c r="E60" s="158" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B59" s="35"/>
-      <c r="C59" s="35"/>
-      <c r="D59" s="34"/>
-      <c r="E59" s="150">
-        <f>SUM(D54:D58)</f>
-        <v>809500</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="35" t="s">
+      <c r="B61" s="35"/>
+      <c r="C61" s="35"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="150">
+        <f>SUM(D54:D60)</f>
+        <v>1281433.4099999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B60" s="67"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="173"/>
-      <c r="E60" s="149"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="5" t="s">
+      <c r="B62" s="67"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="173"/>
+      <c r="E62" s="149"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="157">
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="157">
         <v>58300</v>
       </c>
-      <c r="E61" s="151"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="5" t="s">
+      <c r="E63" s="151"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="157">
-        <v>81498.02</v>
-      </c>
-      <c r="E62" s="40"/>
-    </row>
-    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="51" t="s">
-        <v>16</v>
-      </c>
-      <c r="B63" s="51"/>
-      <c r="C63" s="51"/>
-      <c r="D63" s="109"/>
-      <c r="E63" s="103">
-        <f>SUM(D61:D62)</f>
-        <v>139798.02000000002</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
-      <c r="D64" s="102"/>
-      <c r="E64" s="110"/>
+      <c r="D64" s="157">
+        <v>81498.02</v>
+      </c>
+      <c r="E64" s="40"/>
     </row>
     <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="30" t="s">
+      <c r="A65" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B65" s="51"/>
+      <c r="C65" s="51"/>
+      <c r="D65" s="109"/>
+      <c r="E65" s="103">
+        <f>SUM(D63:D64)</f>
+        <v>139798.02000000002</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="5"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="102"/>
+      <c r="E66" s="110"/>
+    </row>
+    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="B65" s="30"/>
-      <c r="C65" s="30"/>
-      <c r="D65" s="111"/>
-      <c r="E65" s="112"/>
-    </row>
-    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="1"/>
-      <c r="D66" s="113"/>
-      <c r="E66" s="114"/>
-      <c r="F66" s="43"/>
-    </row>
-    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="3" t="s">
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="111"/>
+      <c r="E67" s="112"/>
+    </row>
+    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="1"/>
+      <c r="D68" s="113"/>
+      <c r="E68" s="114"/>
+      <c r="F68" s="43"/>
+    </row>
+    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B67" s="10"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="115"/>
-      <c r="E67" s="116">
-        <f>(SUM(E27:E65))</f>
-        <v>4268911.0500000007</v>
-      </c>
-      <c r="F67" s="138"/>
-      <c r="G67" s="43"/>
-      <c r="H67" s="124"/>
-      <c r="I67" s="124"/>
-      <c r="J67" s="124"/>
-      <c r="K67" s="124"/>
-      <c r="L67" s="124"/>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D68" s="113"/>
-      <c r="E68" s="113"/>
-      <c r="H68" s="124"/>
-      <c r="I68" s="124"/>
-      <c r="J68" s="124"/>
-      <c r="K68" s="124"/>
-      <c r="L68" s="124"/>
-    </row>
-    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D69" s="113"/>
-      <c r="E69" s="113"/>
-      <c r="H69" s="162"/>
+      <c r="B69" s="10"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="115"/>
+      <c r="E69" s="116">
+        <f>(SUM(E27:E67))</f>
+        <v>5437442.1600000001</v>
+      </c>
+      <c r="F69" s="138"/>
+      <c r="G69" s="43"/>
+      <c r="H69" s="124"/>
+      <c r="I69" s="124"/>
+      <c r="J69" s="124"/>
+      <c r="K69" s="124"/>
+      <c r="L69" s="124"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A70" s="11" t="s">
+      <c r="D70" s="113"/>
+      <c r="E70" s="113"/>
+      <c r="H70" s="124"/>
+      <c r="I70" s="124"/>
+      <c r="J70" s="124"/>
+      <c r="K70" s="124"/>
+      <c r="L70" s="124"/>
+    </row>
+    <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D71" s="113"/>
+      <c r="E71" s="113"/>
+      <c r="H71" s="162"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B70" s="12"/>
-      <c r="C70" s="13"/>
-      <c r="D70" s="117"/>
-      <c r="E70" s="118"/>
-    </row>
-    <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="199"/>
-      <c r="B71" s="200"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="128"/>
-      <c r="E71" s="104"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A72" s="199"/>
-      <c r="B72" s="200"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="106"/>
-      <c r="E72" s="104"/>
-    </row>
-    <row r="73" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="193"/>
-      <c r="B73" s="194"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="117"/>
+      <c r="E72" s="118"/>
+    </row>
+    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="200"/>
+      <c r="B73" s="201"/>
       <c r="C73" s="5"/>
-      <c r="D73" s="106"/>
+      <c r="D73" s="128"/>
       <c r="E73" s="104"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="105"/>
-      <c r="B74" s="107"/>
+      <c r="A74" s="200"/>
+      <c r="B74" s="201"/>
       <c r="C74" s="5"/>
       <c r="D74" s="106"/>
       <c r="E74" s="104"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" s="49"/>
-      <c r="B75" s="48"/>
-      <c r="C75" s="48"/>
-      <c r="D75" s="58"/>
-      <c r="E75" s="58">
-        <f>SUM(D71:D74)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="77" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="78" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="30" t="s">
+    <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="202"/>
+      <c r="B75" s="203"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="106"/>
+      <c r="E75" s="104"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="105"/>
+      <c r="B76" s="107"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="106"/>
+      <c r="E76" s="104"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="49"/>
+      <c r="B77" s="48"/>
+      <c r="C77" s="48"/>
+      <c r="D77" s="58"/>
+      <c r="E77" s="58">
+        <f>SUM(D73:D76)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="B78" s="30"/>
-      <c r="C78" s="30"/>
-      <c r="D78" s="31"/>
-      <c r="E78" s="101"/>
-    </row>
-    <row r="79" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B80" s="10"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="68">
-        <f>E75+E78</f>
-        <v>0</v>
-      </c>
+      <c r="B80" s="30"/>
+      <c r="C80" s="30"/>
+      <c r="D80" s="31"/>
+      <c r="E80" s="101"/>
     </row>
     <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="99" t="s">
-        <v>14</v>
-      </c>
-      <c r="B82" s="100">
-        <f>E67</f>
-        <v>4268911.0500000007</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" s="100">
-        <f>E67-E65</f>
-        <v>4268911.0500000007</v>
-      </c>
-    </row>
+      <c r="A82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B82" s="10"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="68">
+        <f>E77+E80</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="99" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B84" s="100">
-        <f>E80-E78</f>
-        <v>0</v>
+        <f>E69</f>
+        <v>5437442.1600000001</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" s="100">
+        <f>E69-E67</f>
+        <v>5437442.1600000001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="99" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" s="100">
+        <f>E82-E80</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="B85" s="100">
-        <f>E80</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D87" s="124"/>
-      <c r="E87" s="124"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D88" s="124"/>
-      <c r="E88" s="124"/>
-    </row>
-    <row r="89" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="23" t="s">
+      <c r="B87" s="100">
+        <f>E82</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D89" s="124"/>
+      <c r="E89" s="124"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D90" s="124"/>
+      <c r="E90" s="124"/>
+    </row>
+    <row r="91" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="B89" s="125"/>
-      <c r="C89" s="24"/>
-    </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="33"/>
-      <c r="B90" s="59">
-        <v>0</v>
-      </c>
-      <c r="C90" s="26"/>
-    </row>
-    <row r="91" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="25" t="s">
+      <c r="B91" s="125"/>
+      <c r="C91" s="24"/>
+    </row>
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="33"/>
+      <c r="B92" s="59">
+        <v>0</v>
+      </c>
+      <c r="C92" s="26"/>
+    </row>
+    <row r="93" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B91" s="40">
+      <c r="B93" s="40">
         <f>PRORRATEO!F29</f>
         <v>3651399.3100000005</v>
       </c>
-      <c r="C91" s="24"/>
-    </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="25"/>
-      <c r="B92" s="40">
-        <v>0</v>
-      </c>
-      <c r="C92" s="24"/>
-    </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="25" t="s">
+      <c r="C93" s="24"/>
+    </row>
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="25"/>
+      <c r="B94" s="40">
+        <v>0</v>
+      </c>
+      <c r="C94" s="24"/>
+    </row>
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="B93" s="108">
-        <f>B114</f>
-        <v>0</v>
-      </c>
-      <c r="C93" s="24"/>
-    </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="28"/>
-      <c r="B94" s="47"/>
-      <c r="C94" s="24"/>
-    </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="123" t="s">
+      <c r="B95" s="108">
+        <f>B118</f>
+        <v>0</v>
+      </c>
+      <c r="C95" s="24"/>
+    </row>
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="28"/>
+      <c r="B96" s="47"/>
+      <c r="C96" s="24"/>
+    </row>
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="B95" s="47"/>
-      <c r="C95" s="24"/>
-    </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="39" t="s">
+      <c r="B97" s="47"/>
+      <c r="C97" s="24"/>
+    </row>
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="B96" s="47">
-        <f>-B83</f>
-        <v>-4268911.0500000007</v>
-      </c>
-      <c r="C96" s="24"/>
-    </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="28" t="s">
+      <c r="B98" s="47">
+        <f>-B85</f>
+        <v>-5437442.1600000001</v>
+      </c>
+      <c r="C98" s="24"/>
+    </row>
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B97" s="47">
-        <f>-(B84)</f>
-        <v>0</v>
-      </c>
-      <c r="C97" s="24"/>
-    </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="32" t="s">
+      <c r="B99" s="47">
+        <f>-(B86)</f>
+        <v>0</v>
+      </c>
+      <c r="C99" s="24"/>
+    </row>
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="B98" s="59">
-        <f>SUM(B90:B97)</f>
-        <v>-617511.74000000022</v>
-      </c>
-      <c r="C98" s="27"/>
-      <c r="D98" s="43"/>
-    </row>
-    <row r="99" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B99" s="41"/>
-      <c r="C99" s="27"/>
-      <c r="D99" s="43"/>
-      <c r="E99" s="126"/>
-      <c r="F99" s="127"/>
-    </row>
-    <row r="100" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B100" s="42"/>
+      <c r="B100" s="59">
+        <f>SUM(B92:B99)</f>
+        <v>-1786042.8499999996</v>
+      </c>
       <c r="C100" s="27"/>
-    </row>
-    <row r="101" spans="1:6" s="38" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101"/>
+      <c r="D100" s="43"/>
+    </row>
+    <row r="101" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="41"/>
-      <c r="C101" s="37"/>
-    </row>
-    <row r="102" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="131" t="s">
+      <c r="C101" s="27"/>
+      <c r="D101" s="43"/>
+      <c r="E101" s="126"/>
+      <c r="F101" s="127"/>
+    </row>
+    <row r="102" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B102" s="42"/>
+      <c r="C102" s="27"/>
+    </row>
+    <row r="103" spans="1:6" s="38" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103"/>
+      <c r="B103" s="41"/>
+      <c r="C103" s="37"/>
+    </row>
+    <row r="104" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="131" t="s">
         <v>85</v>
       </c>
-      <c r="B102" s="184">
+      <c r="B104" s="184">
         <v>-1101016.7960999962</v>
       </c>
-      <c r="C102" s="37"/>
-      <c r="D102" s="46"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="B103" s="136">
-        <f>-B83</f>
-        <v>-4268911.0500000007</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="B104" s="136">
-        <f>-B84</f>
-        <v>0</v>
-      </c>
+      <c r="C104" s="37"/>
+      <c r="D104" s="46"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="54" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="B105" s="136">
-        <f>B114</f>
-        <v>0</v>
+        <f>-B85</f>
+        <v>-5437442.1600000001</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="B106" s="136">
+        <f>-B86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A107" s="54" t="s">
+        <v>128</v>
+      </c>
+      <c r="B107" s="232">
+        <v>-99500</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="54" t="s">
+        <v>129</v>
+      </c>
+      <c r="B108" s="232">
+        <v>-24000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="B109" s="136">
+        <f>B118</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="B106" s="137">
+      <c r="B110" s="137">
         <f>PRORRATEO!F29</f>
         <v>3651399.3100000005</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="134" t="s">
+    <row r="111" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="134" t="s">
         <v>48</v>
       </c>
-      <c r="B107" s="135">
-        <f>SUM(B102:C106)</f>
-        <v>-1718528.5360999964</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="132"/>
-      <c r="B108" s="132"/>
-    </row>
-    <row r="109" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="202" t="s">
+      <c r="B111" s="135">
+        <f>SUM(B104:C110)</f>
+        <v>-3010559.6460999958</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="132"/>
+      <c r="B112" s="132"/>
+    </row>
+    <row r="113" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A114" s="199" t="s">
         <v>32</v>
       </c>
-      <c r="B110" s="202"/>
-      <c r="C110" s="202"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="202"/>
-      <c r="B111" s="202"/>
-      <c r="C111" s="202"/>
-    </row>
-    <row r="112" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="120"/>
-      <c r="B112" s="36"/>
-      <c r="C112" s="36">
+      <c r="B114" s="199"/>
+      <c r="C114" s="199"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A115" s="199"/>
+      <c r="B115" s="199"/>
+      <c r="C115" s="199"/>
+    </row>
+    <row r="116" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="120"/>
+      <c r="B116" s="36"/>
+      <c r="C116" s="36">
         <v>40000</v>
       </c>
-      <c r="E112" s="138"/>
-    </row>
-    <row r="113" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="120"/>
-      <c r="B113" s="122"/>
-      <c r="C113" s="119"/>
-      <c r="D113" s="138"/>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A114" s="44" t="s">
+      <c r="E116" s="138"/>
+    </row>
+    <row r="117" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="120"/>
+      <c r="B117" s="122"/>
+      <c r="C117" s="119"/>
+      <c r="D117" s="138"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A118" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="B114" s="121">
-        <f>SUM(B112:B113)</f>
-        <v>0</v>
-      </c>
-      <c r="C114" s="45"/>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M115" s="8"/>
-    </row>
-    <row r="116" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="201"/>
-      <c r="B116" s="201"/>
-      <c r="C116" s="201"/>
-      <c r="D116" s="201"/>
-      <c r="E116" s="201"/>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A117" s="201"/>
-      <c r="B117" s="201"/>
-      <c r="C117" s="201"/>
-      <c r="D117" s="201"/>
-      <c r="E117" s="201"/>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A118" s="201"/>
-      <c r="B118" s="201"/>
-      <c r="C118" s="201"/>
-      <c r="D118" s="201"/>
-      <c r="E118" s="201"/>
+      <c r="B118" s="121">
+        <f>SUM(B116:B117)</f>
+        <v>0</v>
+      </c>
+      <c r="C118" s="45"/>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="201"/>
-      <c r="B119" s="201"/>
-      <c r="C119" s="201"/>
-      <c r="D119" s="201"/>
-      <c r="E119" s="201"/>
+      <c r="M119" s="8"/>
+    </row>
+    <row r="120" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="198"/>
+      <c r="B120" s="198"/>
+      <c r="C120" s="198"/>
+      <c r="D120" s="198"/>
+      <c r="E120" s="198"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A121" s="198"/>
+      <c r="B121" s="198"/>
+      <c r="C121" s="198"/>
+      <c r="D121" s="198"/>
+      <c r="E121" s="198"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A122" s="198"/>
+      <c r="B122" s="198"/>
+      <c r="C122" s="198"/>
+      <c r="D122" s="198"/>
+      <c r="E122" s="198"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A123" s="198"/>
+      <c r="B123" s="198"/>
+      <c r="C123" s="198"/>
+      <c r="D123" s="198"/>
+      <c r="E123" s="198"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A116:E119"/>
-    <mergeCell ref="A110:C111"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A56:B56"/>
+  <mergeCells count="17">
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A120:E123"/>
+    <mergeCell ref="A114:C115"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A75:B75"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2941,15 +3003,15 @@
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="205"/>
-      <c r="E1" s="205"/>
-      <c r="F1" s="205"/>
-      <c r="G1" s="205"/>
-      <c r="H1" s="205"/>
-      <c r="I1" s="205"/>
-      <c r="J1" s="205"/>
-      <c r="K1" s="205"/>
-      <c r="L1" s="205"/>
+      <c r="D1" s="213"/>
+      <c r="E1" s="213"/>
+      <c r="F1" s="213"/>
+      <c r="G1" s="213"/>
+      <c r="H1" s="213"/>
+      <c r="I1" s="213"/>
+      <c r="J1" s="213"/>
+      <c r="K1" s="213"/>
+      <c r="L1" s="213"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
@@ -2996,46 +3058,46 @@
       <c r="N3" s="60"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="210" t="s">
+      <c r="A4" s="208" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="210" t="s">
+      <c r="B4" s="208" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="210" t="s">
+      <c r="C4" s="208" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="210" t="s">
+      <c r="D4" s="208" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="206" t="s">
+      <c r="E4" s="214" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="210" t="s">
+      <c r="F4" s="208" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="212" t="s">
+      <c r="G4" s="218" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="206" t="s">
+      <c r="H4" s="214" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="206" t="s">
+      <c r="I4" s="214" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="206" t="s">
+      <c r="J4" s="214" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="215" t="s">
+      <c r="K4" s="221" t="s">
         <v>80</v>
       </c>
       <c r="L4" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="208" t="s">
+      <c r="M4" s="216" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="203" t="s">
+      <c r="N4" s="211" t="s">
         <v>36</v>
       </c>
       <c r="Q4" s="130">
@@ -3043,23 +3105,23 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="211"/>
-      <c r="B5" s="211"/>
-      <c r="C5" s="217"/>
-      <c r="D5" s="211"/>
-      <c r="E5" s="207"/>
-      <c r="F5" s="211"/>
-      <c r="G5" s="213"/>
-      <c r="H5" s="207"/>
-      <c r="I5" s="214"/>
-      <c r="J5" s="207"/>
-      <c r="K5" s="216"/>
+      <c r="A5" s="210"/>
+      <c r="B5" s="210"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="210"/>
+      <c r="E5" s="215"/>
+      <c r="F5" s="210"/>
+      <c r="G5" s="219"/>
+      <c r="H5" s="215"/>
+      <c r="I5" s="220"/>
+      <c r="J5" s="215"/>
+      <c r="K5" s="222"/>
       <c r="L5" s="61" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 18/06</v>
-      </c>
-      <c r="M5" s="209"/>
-      <c r="N5" s="204"/>
+        <v>VTO 17/07</v>
+      </c>
+      <c r="M5" s="217"/>
+      <c r="N5" s="212"/>
     </row>
     <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="64">
@@ -3778,11 +3840,11 @@
       </c>
     </row>
     <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="224">
+      <c r="A19" s="193">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="B19" s="224" t="s">
+      <c r="B19" s="193" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="65"/>
@@ -4217,93 +4279,88 @@
     </row>
     <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="201" t="str">
+      <c r="B32" s="198" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="201"/>
-      <c r="D32" s="201"/>
-      <c r="E32" s="201"/>
-      <c r="F32" s="201"/>
-      <c r="G32" s="201"/>
-      <c r="H32" s="201"/>
-      <c r="I32" s="201"/>
-      <c r="J32" s="201"/>
-      <c r="K32" s="201"/>
-      <c r="L32" s="201"/>
+      <c r="C32" s="198"/>
+      <c r="D32" s="198"/>
+      <c r="E32" s="198"/>
+      <c r="F32" s="198"/>
+      <c r="G32" s="198"/>
+      <c r="H32" s="198"/>
+      <c r="I32" s="198"/>
+      <c r="J32" s="198"/>
+      <c r="K32" s="198"/>
+      <c r="L32" s="198"/>
     </row>
     <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="201"/>
-      <c r="C33" s="201"/>
-      <c r="D33" s="201"/>
-      <c r="E33" s="201"/>
-      <c r="F33" s="201"/>
-      <c r="G33" s="201"/>
-      <c r="H33" s="201"/>
-      <c r="I33" s="201"/>
-      <c r="J33" s="201"/>
-      <c r="K33" s="201"/>
-      <c r="L33" s="201"/>
+      <c r="B33" s="198"/>
+      <c r="C33" s="198"/>
+      <c r="D33" s="198"/>
+      <c r="E33" s="198"/>
+      <c r="F33" s="198"/>
+      <c r="G33" s="198"/>
+      <c r="H33" s="198"/>
+      <c r="I33" s="198"/>
+      <c r="J33" s="198"/>
+      <c r="K33" s="198"/>
+      <c r="L33" s="198"/>
     </row>
     <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="201"/>
-      <c r="C34" s="201"/>
-      <c r="D34" s="201"/>
-      <c r="E34" s="201"/>
-      <c r="F34" s="201"/>
-      <c r="G34" s="201"/>
-      <c r="H34" s="201"/>
-      <c r="I34" s="201"/>
-      <c r="J34" s="201"/>
-      <c r="K34" s="201"/>
-      <c r="L34" s="201"/>
+      <c r="B34" s="198"/>
+      <c r="C34" s="198"/>
+      <c r="D34" s="198"/>
+      <c r="E34" s="198"/>
+      <c r="F34" s="198"/>
+      <c r="G34" s="198"/>
+      <c r="H34" s="198"/>
+      <c r="I34" s="198"/>
+      <c r="J34" s="198"/>
+      <c r="K34" s="198"/>
+      <c r="L34" s="198"/>
     </row>
     <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="201"/>
-      <c r="C35" s="201"/>
-      <c r="D35" s="201"/>
-      <c r="E35" s="201"/>
-      <c r="F35" s="201"/>
-      <c r="G35" s="201"/>
-      <c r="H35" s="201"/>
-      <c r="I35" s="201"/>
-      <c r="J35" s="201"/>
-      <c r="K35" s="201"/>
-      <c r="L35" s="201"/>
+      <c r="B35" s="198"/>
+      <c r="C35" s="198"/>
+      <c r="D35" s="198"/>
+      <c r="E35" s="198"/>
+      <c r="F35" s="198"/>
+      <c r="G35" s="198"/>
+      <c r="H35" s="198"/>
+      <c r="I35" s="198"/>
+      <c r="J35" s="198"/>
+      <c r="K35" s="198"/>
+      <c r="L35" s="198"/>
     </row>
     <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="201"/>
-      <c r="C36" s="201"/>
-      <c r="D36" s="201"/>
-      <c r="E36" s="201"/>
-      <c r="F36" s="201"/>
-      <c r="G36" s="201"/>
-      <c r="H36" s="201"/>
-      <c r="I36" s="201"/>
-      <c r="J36" s="201"/>
-      <c r="K36" s="201"/>
-      <c r="L36" s="201"/>
+      <c r="B36" s="198"/>
+      <c r="C36" s="198"/>
+      <c r="D36" s="198"/>
+      <c r="E36" s="198"/>
+      <c r="F36" s="198"/>
+      <c r="G36" s="198"/>
+      <c r="H36" s="198"/>
+      <c r="I36" s="198"/>
+      <c r="J36" s="198"/>
+      <c r="K36" s="198"/>
+      <c r="L36" s="198"/>
     </row>
     <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="201"/>
-      <c r="C37" s="201"/>
-      <c r="D37" s="201"/>
-      <c r="E37" s="201"/>
-      <c r="F37" s="201"/>
-      <c r="G37" s="201"/>
-      <c r="H37" s="201"/>
-      <c r="I37" s="201"/>
-      <c r="J37" s="201"/>
-      <c r="K37" s="201"/>
-      <c r="L37" s="201"/>
+      <c r="B37" s="198"/>
+      <c r="C37" s="198"/>
+      <c r="D37" s="198"/>
+      <c r="E37" s="198"/>
+      <c r="F37" s="198"/>
+      <c r="G37" s="198"/>
+      <c r="H37" s="198"/>
+      <c r="I37" s="198"/>
+      <c r="J37" s="198"/>
+      <c r="K37" s="198"/>
+      <c r="L37" s="198"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B32:L37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="H4:H5"/>
@@ -4314,6 +4371,11 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
+    <mergeCell ref="B32:L37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4328,7 +4390,7 @@
     <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B2" s="189" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C2" s="190">
         <v>1</v>
@@ -4339,56 +4401,56 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B3" s="191" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C3" s="192" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="F3" s="187"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="218" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" s="219"/>
-      <c r="D4" s="219"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="220"/>
+      <c r="B4" s="223" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="224"/>
+      <c r="D4" s="224"/>
+      <c r="E4" s="224"/>
+      <c r="F4" s="225"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="218"/>
-      <c r="C5" s="219"/>
-      <c r="D5" s="219"/>
-      <c r="E5" s="219"/>
-      <c r="F5" s="220"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="224"/>
+      <c r="D5" s="224"/>
+      <c r="E5" s="224"/>
+      <c r="F5" s="225"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="124"/>
-      <c r="B6" s="218"/>
-      <c r="C6" s="219"/>
-      <c r="D6" s="219"/>
-      <c r="E6" s="219"/>
-      <c r="F6" s="220"/>
+      <c r="B6" s="223"/>
+      <c r="C6" s="224"/>
+      <c r="D6" s="224"/>
+      <c r="E6" s="224"/>
+      <c r="F6" s="225"/>
       <c r="N6" s="124"/>
       <c r="O6" s="124"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="124"/>
-      <c r="B7" s="218"/>
-      <c r="C7" s="219"/>
-      <c r="D7" s="219"/>
-      <c r="E7" s="219"/>
-      <c r="F7" s="220"/>
+      <c r="B7" s="223"/>
+      <c r="C7" s="224"/>
+      <c r="D7" s="224"/>
+      <c r="E7" s="224"/>
+      <c r="F7" s="225"/>
       <c r="N7" s="124"/>
       <c r="O7" s="124"/>
     </row>
     <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="124"/>
-      <c r="B8" s="221"/>
-      <c r="C8" s="222"/>
-      <c r="D8" s="222"/>
-      <c r="E8" s="222"/>
-      <c r="F8" s="223"/>
+      <c r="B8" s="226"/>
+      <c r="C8" s="227"/>
+      <c r="D8" s="227"/>
+      <c r="E8" s="227"/>
+      <c r="F8" s="228"/>
       <c r="N8" s="124"/>
       <c r="O8" s="124"/>
     </row>
@@ -4399,10 +4461,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="124"/>
-      <c r="B10" s="225" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" s="226">
+      <c r="B10" s="194" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="195">
         <v>1</v>
       </c>
       <c r="D10" s="185"/>
@@ -4413,52 +4475,52 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="124"/>
-      <c r="B11" s="227" t="s">
-        <v>120</v>
-      </c>
-      <c r="C11" s="228" t="s">
-        <v>123</v>
+      <c r="B11" s="196" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" s="197" t="s">
+        <v>113</v>
       </c>
       <c r="F11" s="187"/>
       <c r="N11" s="124"/>
       <c r="O11" s="124"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B12" s="218" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="219"/>
-      <c r="D12" s="219"/>
-      <c r="E12" s="219"/>
-      <c r="F12" s="220"/>
+      <c r="B12" s="223" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="224"/>
+      <c r="D12" s="224"/>
+      <c r="E12" s="224"/>
+      <c r="F12" s="225"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="218"/>
-      <c r="C13" s="219"/>
-      <c r="D13" s="219"/>
-      <c r="E13" s="219"/>
-      <c r="F13" s="220"/>
+      <c r="B13" s="223"/>
+      <c r="C13" s="224"/>
+      <c r="D13" s="224"/>
+      <c r="E13" s="224"/>
+      <c r="F13" s="225"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="218"/>
-      <c r="C14" s="219"/>
-      <c r="D14" s="219"/>
-      <c r="E14" s="219"/>
-      <c r="F14" s="220"/>
+      <c r="B14" s="223"/>
+      <c r="C14" s="224"/>
+      <c r="D14" s="224"/>
+      <c r="E14" s="224"/>
+      <c r="F14" s="225"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="218"/>
-      <c r="C15" s="219"/>
-      <c r="D15" s="219"/>
-      <c r="E15" s="219"/>
-      <c r="F15" s="220"/>
+      <c r="B15" s="223"/>
+      <c r="C15" s="224"/>
+      <c r="D15" s="224"/>
+      <c r="E15" s="224"/>
+      <c r="F15" s="225"/>
     </row>
     <row r="16" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="221"/>
-      <c r="C16" s="222"/>
-      <c r="D16" s="222"/>
-      <c r="E16" s="222"/>
-      <c r="F16" s="223"/>
+      <c r="B16" s="226"/>
+      <c r="C16" s="227"/>
+      <c r="D16" s="227"/>
+      <c r="E16" s="227"/>
+      <c r="F16" s="228"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026/YRIGOYEN 7630/Junio/YRIGOYEN7630-Junio.xlsx
+++ b/2026/YRIGOYEN 7630/Junio/YRIGOYEN7630-Junio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEDAD97-B4A7-4D84-9AFE-86A819CC9663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BF3A21-37EF-48B7-A276-DD0DF0086540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,15 +18,20 @@
     <sheet name="ANOTACIONES" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$119</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$120</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="133">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -341,21 +346,12 @@
     <t>Transf 22/05</t>
   </si>
   <si>
-    <t>Debito 11/05</t>
-  </si>
-  <si>
-    <t>Debito 18/05</t>
-  </si>
-  <si>
     <t>Subidos en Juni0 a 165000</t>
   </si>
   <si>
     <t>Cuello Natalia - Limpieza de columna cocina y baño de todas las UF - Cuota 3/5</t>
   </si>
   <si>
-    <t>Transf 26/05</t>
-  </si>
-  <si>
     <t>Anotacion:</t>
   </si>
   <si>
@@ -386,18 +382,12 @@
     <t>Sindicatos mes de JUNIO</t>
   </si>
   <si>
-    <t>Honorarios administracion - MAYO y JUNIO</t>
-  </si>
-  <si>
     <t>Transf 24/06</t>
   </si>
   <si>
     <t>Transf 05/06</t>
   </si>
   <si>
-    <t xml:space="preserve">Kromacolor </t>
-  </si>
-  <si>
     <t>Transf 13/06</t>
   </si>
   <si>
@@ -417,6 +407,30 @@
   </si>
   <si>
     <t>Envio Carta documento - Correo Argentino</t>
+  </si>
+  <si>
+    <t>Debito 02/06</t>
+  </si>
+  <si>
+    <t>Debito 08/06</t>
+  </si>
+  <si>
+    <t>Debito 16/06</t>
+  </si>
+  <si>
+    <t>Debito 12/06</t>
+  </si>
+  <si>
+    <t>Kromacolor - Compra de pintura recuplast</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Se adeuda  JUNIO</t>
+  </si>
+  <si>
+    <t>Gastos part</t>
+  </si>
+  <si>
+    <t>(Incluye SAC)</t>
   </si>
 </sst>
 </file>
@@ -433,7 +447,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -615,14 +629,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -630,7 +636,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -709,6 +715,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -1121,7 +1133,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="233">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1271,7 +1283,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1361,116 +1372,96 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="24" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="24" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="25" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1489,12 +1480,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="20" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="14" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="14" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="14" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="19" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="19" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1573,9 +1595,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1613,9 +1635,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1648,9 +1670,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1683,9 +1722,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1859,22 +1915,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M123"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M124"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="15"/>
       <c r="B1" s="69" t="s">
         <v>54</v>
@@ -1883,7 +1939,7 @@
       <c r="D1" s="69"/>
       <c r="E1" s="70"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
       <c r="B2" s="71" t="s">
         <v>28</v>
@@ -1892,16 +1948,16 @@
       <c r="D2" s="71"/>
       <c r="E2" s="72"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
-      <c r="B3" s="204" t="s">
+      <c r="B3" s="183" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="204"/>
-      <c r="D3" s="204"/>
-      <c r="E3" s="205"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="184"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>0</v>
       </c>
@@ -1912,12 +1968,12 @@
       <c r="D4" s="20"/>
       <c r="E4" s="21"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="71" t="s">
@@ -1925,7 +1981,7 @@
       </c>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>90</v>
       </c>
@@ -1936,57 +1992,57 @@
       </c>
       <c r="E6" s="21"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="207" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="207"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="207"/>
-      <c r="C9" s="207"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="207"/>
-      <c r="C10" s="207"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="206" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="186" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="186"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="186"/>
+      <c r="C9" s="186"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="186"/>
+      <c r="C10" s="186"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="185" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="206"/>
-      <c r="C13" s="206"/>
-      <c r="D13" s="206"/>
-      <c r="E13" s="206"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="206"/>
-      <c r="B14" s="206"/>
-      <c r="C14" s="206"/>
-      <c r="D14" s="206"/>
-      <c r="E14" s="206"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="206"/>
-      <c r="B15" s="206"/>
-      <c r="C15" s="206"/>
-      <c r="D15" s="206"/>
-      <c r="E15" s="206"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="206"/>
-      <c r="B16" s="206"/>
-      <c r="C16" s="206"/>
-      <c r="D16" s="206"/>
-      <c r="E16" s="206"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="185"/>
+      <c r="C13" s="185"/>
+      <c r="D13" s="185"/>
+      <c r="E13" s="185"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="185"/>
+      <c r="B14" s="185"/>
+      <c r="C14" s="185"/>
+      <c r="D14" s="185"/>
+      <c r="E14" s="185"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="185"/>
+      <c r="B15" s="185"/>
+      <c r="C15" s="185"/>
+      <c r="D15" s="185"/>
+      <c r="E15" s="185"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="185"/>
+      <c r="B16" s="185"/>
+      <c r="C16" s="185"/>
+      <c r="D16" s="185"/>
+      <c r="E16" s="185"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>10</v>
       </c>
@@ -1995,7 +2051,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="14"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="35" t="s">
         <v>34</v>
       </c>
@@ -2004,630 +2060,626 @@
       <c r="D21" s="34"/>
       <c r="E21" s="34"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="C22" s="5"/>
-      <c r="D22" s="169">
+      <c r="D22" s="224">
         <v>1561247</v>
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="169"/>
+      <c r="D23" s="224"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="57" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="57"/>
       <c r="C24" s="57"/>
-      <c r="D24" s="170">
+      <c r="D24" s="225">
         <f>SUM(D22:D23)</f>
         <v>1561247</v>
       </c>
-      <c r="E24" s="139"/>
+      <c r="E24" s="138"/>
       <c r="G24" s="22"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="169"/>
+      <c r="D25" s="224"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>96</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="169">
+      <c r="D26" s="224">
         <v>0</v>
       </c>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>97</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="169">
+      <c r="D27" s="224">
         <v>0</v>
       </c>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="171"/>
+      <c r="D28" s="226"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="57" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="57"/>
       <c r="C29" s="57"/>
-      <c r="D29" s="172">
+      <c r="D29" s="227">
         <f>SUM(D25:D28)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="139"/>
-    </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E29" s="138"/>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="29" t="s">
         <v>1</v>
       </c>
       <c r="B30" s="29"/>
       <c r="C30" s="29"/>
-      <c r="D30" s="173"/>
-      <c r="E30" s="140">
+      <c r="D30" s="228"/>
+      <c r="E30" s="139">
         <f>D24+D29</f>
         <v>1561247</v>
       </c>
       <c r="F30" s="22"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="35" t="s">
         <v>19</v>
       </c>
       <c r="B31" s="35"/>
       <c r="C31" s="35"/>
-      <c r="D31" s="174"/>
-      <c r="E31" s="141"/>
-    </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="202" t="s">
-        <v>117</v>
-      </c>
-      <c r="B32" s="203"/>
+      <c r="D31" s="229"/>
+      <c r="E31" s="140"/>
+    </row>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="181" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="182"/>
       <c r="C32" s="52"/>
-      <c r="D32" s="231">
+      <c r="D32" s="224">
         <v>45000</v>
       </c>
-      <c r="E32" s="142"/>
-    </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="202" t="s">
-        <v>119</v>
-      </c>
-      <c r="B33" s="203"/>
+      <c r="E32" s="141"/>
+    </row>
+    <row r="33" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="181" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" s="182"/>
       <c r="C33" s="52"/>
-      <c r="D33" s="175">
-        <f>147300*2</f>
-        <v>294600</v>
-      </c>
-      <c r="E33" s="142"/>
-      <c r="H33" s="152" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D33" s="230">
+        <v>0</v>
+      </c>
+      <c r="E33" s="141"/>
+      <c r="H33" s="151" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="29" t="s">
         <v>16</v>
       </c>
       <c r="B34" s="29"/>
       <c r="C34" s="29"/>
-      <c r="D34" s="176"/>
-      <c r="E34" s="143">
+      <c r="D34" s="231"/>
+      <c r="E34" s="142">
         <f>SUM(D32:D33)</f>
-        <v>339600</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="35" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="29"/>
       <c r="C35" s="29"/>
-      <c r="D35" s="177"/>
-      <c r="E35" s="144"/>
-    </row>
-    <row r="36" spans="1:8" s="38" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="200" t="s">
+      <c r="D35" s="232"/>
+      <c r="E35" s="143"/>
+    </row>
+    <row r="36" spans="1:8" s="38" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="187" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="201"/>
+      <c r="B36" s="188"/>
       <c r="C36" s="54"/>
-      <c r="D36" s="178">
+      <c r="D36" s="233">
         <f>26570+7909</f>
         <v>34479</v>
       </c>
-      <c r="E36" s="163" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="202" t="s">
+      <c r="E36" s="162" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="181" t="s">
         <v>89</v>
       </c>
-      <c r="B37" s="203"/>
+      <c r="B37" s="182"/>
       <c r="C37" s="54"/>
-      <c r="D37" s="179">
+      <c r="D37" s="234">
         <v>54278</v>
       </c>
-      <c r="E37" s="145" t="str">
+      <c r="E37" s="144" t="str">
         <f>E36</f>
-        <v>Debito 11/05</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>Debito 02/06</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="29" t="s">
         <v>2</v>
       </c>
       <c r="B38" s="29"/>
       <c r="C38" s="29"/>
-      <c r="D38" s="176"/>
-      <c r="E38" s="146">
+      <c r="D38" s="231"/>
+      <c r="E38" s="145">
         <f>SUM(D36:D37)</f>
         <v>88757</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="147"/>
-      <c r="C39" s="147"/>
-      <c r="D39" s="180"/>
-      <c r="E39" s="148"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="146"/>
+      <c r="C39" s="146"/>
+      <c r="D39" s="235"/>
+      <c r="E39" s="147"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="52"/>
-      <c r="D40" s="230">
+      <c r="D40" s="36">
         <v>707699.22</v>
       </c>
-      <c r="E40" s="163" t="s">
-        <v>104</v>
-      </c>
-      <c r="G40" s="124"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E40" s="162" t="s">
+        <v>126</v>
+      </c>
+      <c r="G40" s="123"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="52"/>
-      <c r="D41" s="181">
+      <c r="D41" s="36">
         <v>10602.27</v>
       </c>
-      <c r="E41" s="154" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E41" s="153" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="52"/>
-      <c r="D42" s="181">
+      <c r="D42" s="36">
         <v>75532.289999999994</v>
       </c>
-      <c r="E42" s="154" t="str">
+      <c r="E42" s="153" t="str">
         <f>E41</f>
-        <v>Debito 18/05</v>
+        <v>Debito 16/06</v>
       </c>
       <c r="F42" s="43">
         <f>D42+D41</f>
         <v>86134.56</v>
       </c>
-      <c r="G42" s="138"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G42" s="137"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
-      <c r="D43" s="229">
-        <v>102476.36</v>
-      </c>
-      <c r="E43" s="154" t="str">
-        <f>E42</f>
-        <v>Debito 18/05</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D43" s="236">
+        <v>6459.31</v>
+      </c>
+      <c r="E43" s="162" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de JUNIO</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
-      <c r="D44" s="229">
+      <c r="D44" s="236">
         <v>106451.98</v>
       </c>
-      <c r="E44" s="155" t="str">
+      <c r="E44" s="154" t="str">
         <f>E43</f>
-        <v>Debito 18/05</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+        <v>Debito 12/06</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="str">
         <f>A44</f>
         <v>Sindicatos mes de JUNIO</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
-      <c r="D45" s="229">
+      <c r="D45" s="236">
         <v>58133.75</v>
       </c>
-      <c r="E45" s="156" t="str">
+      <c r="E45" s="155" t="str">
         <f>E44</f>
-        <v>Debito 18/05</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>Debito 12/06</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B46" s="147"/>
-      <c r="C46" s="147"/>
-      <c r="D46" s="182"/>
-      <c r="E46" s="146">
+      <c r="B46" s="146"/>
+      <c r="C46" s="146"/>
+      <c r="D46" s="237"/>
+      <c r="E46" s="145">
         <f>SUM(D40:D45)</f>
-        <v>1060895.8700000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+        <v>964878.82000000007</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="147"/>
-      <c r="C47" s="147"/>
-      <c r="D47" s="180"/>
-      <c r="E47" s="148"/>
-    </row>
-    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="146"/>
+      <c r="C47" s="146"/>
+      <c r="D47" s="235"/>
+      <c r="E47" s="147"/>
+    </row>
+    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B48" s="157"/>
+      <c r="B48" s="156"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="229">
+      <c r="D48" s="236">
         <v>69293.56</v>
       </c>
-      <c r="E48" s="158" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E48" s="157" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B49" s="157"/>
+      <c r="B49" s="156"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="229">
-        <v>29349.599999999999</v>
-      </c>
-      <c r="E49" s="158" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D49" s="236">
+        <v>0</v>
+      </c>
+      <c r="E49" s="157"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="157">
-        <v>29818.65</v>
-      </c>
-      <c r="E50" s="158" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="200" t="s">
+      <c r="D50" s="236">
+        <v>29348.6</v>
+      </c>
+      <c r="E50" s="157" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="187" t="s">
         <v>75</v>
       </c>
-      <c r="B51" s="201"/>
+      <c r="B51" s="188"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="229">
-        <v>837249.05</v>
-      </c>
-      <c r="E51" s="158" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D51" s="236">
+        <v>848176.88</v>
+      </c>
+      <c r="E51" s="157" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="29" t="s">
         <v>4</v>
       </c>
       <c r="B52" s="29"/>
       <c r="C52" s="29"/>
-      <c r="D52" s="183"/>
-      <c r="E52" s="146">
+      <c r="D52" s="238"/>
+      <c r="E52" s="145">
         <f>SUM(D48:D51)</f>
-        <v>965710.8600000001</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>946819.04</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="35" t="s">
         <v>100</v>
       </c>
       <c r="B53" s="29"/>
       <c r="C53" s="29"/>
-      <c r="D53" s="176"/>
-      <c r="E53" s="149"/>
-    </row>
-    <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="159" t="s">
+      <c r="D53" s="231"/>
+      <c r="E53" s="148"/>
+    </row>
+    <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="158" t="s">
         <v>95</v>
       </c>
-      <c r="B54" s="153"/>
+      <c r="B54" s="152"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="229">
+      <c r="D54" s="236">
         <v>93200</v>
       </c>
-      <c r="E54" s="158" t="s">
+      <c r="E54" s="157" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="158" t="s">
+        <v>94</v>
+      </c>
+      <c r="B55" s="152"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="236">
+        <v>0</v>
+      </c>
+      <c r="E55" s="157"/>
+    </row>
+    <row r="56" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="187" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" s="188"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="239">
+        <v>333100</v>
+      </c>
+      <c r="E56" s="157" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="105" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" s="152"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="239">
+        <v>334393.40999999997</v>
+      </c>
+      <c r="E57" s="157" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="187" t="s">
+        <v>120</v>
+      </c>
+      <c r="B58" s="188"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="239">
+        <v>235000</v>
+      </c>
+      <c r="E58" s="157" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="187" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="159" t="s">
-        <v>94</v>
-      </c>
-      <c r="B55" s="153"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="157">
-        <v>55000</v>
-      </c>
-      <c r="E55" s="158" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="200" t="s">
-        <v>107</v>
-      </c>
-      <c r="B56" s="201"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="106">
-        <v>333100</v>
-      </c>
-      <c r="E56" s="158" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="105" t="s">
+      <c r="B59" s="188"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="239">
+        <v>127640</v>
+      </c>
+      <c r="E59" s="157" t="s">
         <v>122</v>
       </c>
-      <c r="B57" s="153"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="128">
-        <v>334393.40999999997</v>
-      </c>
-      <c r="E57" s="158" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="200" t="s">
-        <v>125</v>
-      </c>
-      <c r="B58" s="201"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="128">
-        <v>235000</v>
-      </c>
-      <c r="E58" s="158" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="200" t="s">
-        <v>126</v>
-      </c>
-      <c r="B59" s="201"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="128">
-        <v>127640</v>
-      </c>
-      <c r="E59" s="158" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="200" t="s">
+    </row>
+    <row r="60" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="187" t="s">
         <v>93</v>
       </c>
-      <c r="B60" s="201"/>
+      <c r="B60" s="188"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="128">
+      <c r="D60" s="239">
         <v>103100</v>
       </c>
-      <c r="E60" s="158" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E60" s="157" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="29" t="s">
         <v>9</v>
       </c>
       <c r="B61" s="35"/>
       <c r="C61" s="35"/>
-      <c r="D61" s="34"/>
-      <c r="E61" s="150">
+      <c r="D61" s="35"/>
+      <c r="E61" s="149">
         <f>SUM(D54:D60)</f>
-        <v>1281433.4099999999</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1226433.4099999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="35" t="s">
         <v>12</v>
       </c>
       <c r="B62" s="67"/>
       <c r="C62" s="29"/>
-      <c r="D62" s="173"/>
-      <c r="E62" s="149"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D62" s="228"/>
+      <c r="E62" s="148"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>87</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="157">
-        <v>58300</v>
-      </c>
-      <c r="E63" s="151"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D63" s="236">
+        <v>67713</v>
+      </c>
+      <c r="E63" s="150"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
-      <c r="D64" s="157">
-        <v>81498.02</v>
+      <c r="D64" s="236">
+        <v>65295.66</v>
       </c>
       <c r="E64" s="40"/>
     </row>
-    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="51" t="s">
         <v>16</v>
       </c>
       <c r="B65" s="51"/>
       <c r="C65" s="51"/>
-      <c r="D65" s="109"/>
+      <c r="D65" s="240"/>
       <c r="E65" s="103">
         <f>SUM(D63:D64)</f>
-        <v>139798.02000000002</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>133008.66</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
       <c r="D66" s="102"/>
-      <c r="E66" s="110"/>
-    </row>
-    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E66" s="109"/>
+    </row>
+    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="30" t="s">
         <v>50</v>
       </c>
       <c r="B67" s="30"/>
       <c r="C67" s="30"/>
-      <c r="D67" s="111"/>
-      <c r="E67" s="112"/>
-    </row>
-    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D67" s="110"/>
+      <c r="E67" s="111"/>
+    </row>
+    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
-      <c r="D68" s="113"/>
-      <c r="E68" s="114"/>
+      <c r="D68" s="112"/>
+      <c r="E68" s="113"/>
       <c r="F68" s="43"/>
     </row>
-    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B69" s="10"/>
       <c r="C69" s="4"/>
-      <c r="D69" s="115"/>
-      <c r="E69" s="116">
+      <c r="D69" s="114"/>
+      <c r="E69" s="115">
         <f>(SUM(E27:E67))</f>
-        <v>5437442.1600000001</v>
-      </c>
-      <c r="F69" s="138"/>
+        <v>4966143.9300000006</v>
+      </c>
+      <c r="F69" s="137"/>
       <c r="G69" s="43"/>
-      <c r="H69" s="124"/>
-      <c r="I69" s="124"/>
-      <c r="J69" s="124"/>
-      <c r="K69" s="124"/>
-      <c r="L69" s="124"/>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D70" s="113"/>
-      <c r="E70" s="113"/>
-      <c r="H70" s="124"/>
-      <c r="I70" s="124"/>
-      <c r="J70" s="124"/>
-      <c r="K70" s="124"/>
-      <c r="L70" s="124"/>
-    </row>
-    <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D71" s="113"/>
-      <c r="E71" s="113"/>
-      <c r="H71" s="162"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H69" s="123"/>
+      <c r="I69" s="123"/>
+      <c r="J69" s="123"/>
+      <c r="K69" s="123"/>
+      <c r="L69" s="123"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D70" s="112"/>
+      <c r="E70" s="112"/>
+      <c r="H70" s="123"/>
+      <c r="I70" s="123"/>
+      <c r="J70" s="123"/>
+      <c r="K70" s="123"/>
+      <c r="L70" s="123"/>
+    </row>
+    <row r="71" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D71" s="112"/>
+      <c r="E71" s="112"/>
+      <c r="H71" s="161"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
         <v>45</v>
       </c>
       <c r="B72" s="12"/>
       <c r="C72" s="13"/>
-      <c r="D72" s="117"/>
-      <c r="E72" s="118"/>
-    </row>
-    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="200"/>
-      <c r="B73" s="201"/>
+      <c r="D72" s="116"/>
+      <c r="E72" s="117"/>
+    </row>
+    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="187"/>
+      <c r="B73" s="188"/>
       <c r="C73" s="5"/>
-      <c r="D73" s="128"/>
+      <c r="D73" s="127"/>
       <c r="E73" s="104"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="200"/>
-      <c r="B74" s="201"/>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" s="187"/>
+      <c r="B74" s="188"/>
       <c r="C74" s="5"/>
       <c r="D74" s="106"/>
       <c r="E74" s="104"/>
     </row>
-    <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="202"/>
-      <c r="B75" s="203"/>
+    <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="181"/>
+      <c r="B75" s="182"/>
       <c r="C75" s="5"/>
       <c r="D75" s="106"/>
       <c r="E75" s="104"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="105"/>
       <c r="B76" s="107"/>
       <c r="C76" s="5"/>
       <c r="D76" s="106"/>
       <c r="E76" s="104"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="49"/>
       <c r="B77" s="48"/>
       <c r="C77" s="48"/>
@@ -2637,9 +2689,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="30" t="s">
         <v>20</v>
       </c>
@@ -2648,8 +2700,8 @@
       <c r="D80" s="31"/>
       <c r="E80" s="101"/>
     </row>
-    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>21</v>
       </c>
@@ -2661,26 +2713,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="99" t="s">
         <v>14</v>
       </c>
       <c r="B84" s="100">
         <f>E69</f>
-        <v>5437442.1600000001</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>4966143.9300000006</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="99" t="s">
         <v>15</v>
       </c>
       <c r="B85" s="100">
         <f>E69-E67</f>
-        <v>5437442.1600000001</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>4966143.9300000006</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="99" t="s">
         <v>22</v>
       </c>
@@ -2689,7 +2741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="99" t="s">
         <v>40</v>
       </c>
@@ -2698,78 +2750,78 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D89" s="124"/>
-      <c r="E89" s="124"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D90" s="124"/>
-      <c r="E90" s="124"/>
-    </row>
-    <row r="91" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D89" s="123"/>
+      <c r="E89" s="123"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D90" s="123"/>
+      <c r="E90" s="123"/>
+    </row>
+    <row r="91" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="B91" s="125"/>
+      <c r="B91" s="124"/>
       <c r="C91" s="24"/>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="33"/>
       <c r="B92" s="59">
         <v>0</v>
       </c>
       <c r="C92" s="26"/>
     </row>
-    <row r="93" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="25" t="s">
         <v>7</v>
       </c>
       <c r="B93" s="40">
         <f>PRORRATEO!F29</f>
-        <v>3651399.3100000005</v>
+        <v>3882232.5900000008</v>
       </c>
       <c r="C93" s="24"/>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="25"/>
       <c r="B94" s="40">
         <v>0</v>
       </c>
       <c r="C94" s="24"/>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="25" t="s">
         <v>41</v>
       </c>
       <c r="B95" s="108">
-        <f>B118</f>
+        <f>B119</f>
         <v>0</v>
       </c>
       <c r="C95" s="24"/>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="28"/>
       <c r="B96" s="47"/>
       <c r="C96" s="24"/>
     </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="123" t="s">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="122" t="s">
         <v>46</v>
       </c>
       <c r="B97" s="47"/>
       <c r="C97" s="24"/>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="39" t="s">
         <v>23</v>
       </c>
       <c r="B98" s="47">
         <f>-B85</f>
-        <v>-5437442.1600000001</v>
+        <v>-4966143.9300000006</v>
       </c>
       <c r="C98" s="24"/>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="28" t="s">
         <v>24</v>
       </c>
@@ -2779,183 +2831,191 @@
       </c>
       <c r="C99" s="24"/>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="32" t="s">
         <v>9</v>
       </c>
       <c r="B100" s="59">
         <f>SUM(B92:B99)</f>
-        <v>-1786042.8499999996</v>
+        <v>-1083911.3399999999</v>
       </c>
       <c r="C100" s="27"/>
       <c r="D100" s="43"/>
     </row>
-    <row r="101" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="41"/>
       <c r="C101" s="27"/>
       <c r="D101" s="43"/>
-      <c r="E101" s="126"/>
-      <c r="F101" s="127"/>
-    </row>
-    <row r="102" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E101" s="125"/>
+      <c r="F101" s="126"/>
+    </row>
+    <row r="102" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="42"/>
       <c r="C102" s="27"/>
     </row>
-    <row r="103" spans="1:6" s="38" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" s="38" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="B103" s="41"/>
       <c r="C103" s="37"/>
     </row>
-    <row r="104" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="131" t="s">
+    <row r="104" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="130" t="s">
         <v>85</v>
       </c>
-      <c r="B104" s="184">
-        <v>-1101016.7960999962</v>
+      <c r="B104" s="168">
+        <v>-1718528.5360999964</v>
       </c>
       <c r="C104" s="37"/>
       <c r="D104" s="46"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="B105" s="136">
+      <c r="B105" s="135">
         <f>-B85</f>
-        <v>-5437442.1600000001</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-4966143.9300000006</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="B106" s="136">
+      <c r="B106" s="135">
         <f>-B86</f>
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="54" t="s">
-        <v>128</v>
-      </c>
-      <c r="B107" s="232">
+        <v>123</v>
+      </c>
+      <c r="B107" s="180">
         <v>-99500</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="54" t="s">
-        <v>129</v>
-      </c>
-      <c r="B108" s="232">
+        <v>124</v>
+      </c>
+      <c r="B108" s="180">
         <v>-24000</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="B109" s="180">
+        <v>-10244</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="B109" s="136">
-        <f>B118</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="54" t="s">
+      <c r="B110" s="135">
+        <f>B119</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="B110" s="137">
+      <c r="B111" s="136">
         <f>PRORRATEO!F29</f>
-        <v>3651399.3100000005</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="134" t="s">
+        <v>3882232.5900000008</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="B111" s="135">
-        <f>SUM(B104:C110)</f>
-        <v>-3010559.6460999958</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="132"/>
-      <c r="B112" s="132"/>
-    </row>
-    <row r="113" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A114" s="199" t="s">
+      <c r="B112" s="134">
+        <f>SUM(B104:C111)</f>
+        <v>-2936183.8760999963</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" s="131"/>
+      <c r="B113" s="131"/>
+    </row>
+    <row r="114" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" s="190" t="s">
         <v>32</v>
       </c>
-      <c r="B114" s="199"/>
-      <c r="C114" s="199"/>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A115" s="199"/>
-      <c r="B115" s="199"/>
-      <c r="C115" s="199"/>
-    </row>
-    <row r="116" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="120"/>
-      <c r="B116" s="36"/>
-      <c r="C116" s="36">
+      <c r="B115" s="190"/>
+      <c r="C115" s="190"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="190"/>
+      <c r="B116" s="190"/>
+      <c r="C116" s="190"/>
+    </row>
+    <row r="117" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="119"/>
+      <c r="B117" s="36"/>
+      <c r="C117" s="36">
         <v>40000</v>
       </c>
-      <c r="E116" s="138"/>
-    </row>
-    <row r="117" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="120"/>
-      <c r="B117" s="122"/>
-      <c r="C117" s="119"/>
-      <c r="D117" s="138"/>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A118" s="44" t="s">
+      <c r="E117" s="137"/>
+    </row>
+    <row r="118" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="119"/>
+      <c r="B118" s="121"/>
+      <c r="C118" s="118"/>
+      <c r="D118" s="137"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="B118" s="121">
-        <f>SUM(B116:B117)</f>
-        <v>0</v>
-      </c>
-      <c r="C118" s="45"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M119" s="8"/>
-    </row>
-    <row r="120" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="198"/>
-      <c r="B120" s="198"/>
-      <c r="C120" s="198"/>
-      <c r="D120" s="198"/>
-      <c r="E120" s="198"/>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A121" s="198"/>
-      <c r="B121" s="198"/>
-      <c r="C121" s="198"/>
-      <c r="D121" s="198"/>
-      <c r="E121" s="198"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A122" s="198"/>
-      <c r="B122" s="198"/>
-      <c r="C122" s="198"/>
-      <c r="D122" s="198"/>
-      <c r="E122" s="198"/>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A123" s="198"/>
-      <c r="B123" s="198"/>
-      <c r="C123" s="198"/>
-      <c r="D123" s="198"/>
-      <c r="E123" s="198"/>
+      <c r="B119" s="120">
+        <f>SUM(B117:B118)</f>
+        <v>0</v>
+      </c>
+      <c r="C119" s="45"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M120" s="8"/>
+    </row>
+    <row r="121" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="189"/>
+      <c r="B121" s="189"/>
+      <c r="C121" s="189"/>
+      <c r="D121" s="189"/>
+      <c r="E121" s="189"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" s="189"/>
+      <c r="B122" s="189"/>
+      <c r="C122" s="189"/>
+      <c r="D122" s="189"/>
+      <c r="E122" s="189"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" s="189"/>
+      <c r="B123" s="189"/>
+      <c r="C123" s="189"/>
+      <c r="D123" s="189"/>
+      <c r="E123" s="189"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" s="189"/>
+      <c r="B124" s="189"/>
+      <c r="C124" s="189"/>
+      <c r="D124" s="189"/>
+      <c r="E124" s="189"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A121:E124"/>
+    <mergeCell ref="A115:C116"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A75:B75"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A51:B51"/>
@@ -2963,11 +3023,11 @@
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A56:B56"/>
     <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A120:E123"/>
-    <mergeCell ref="A114:C115"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2977,45 +3037,46 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:T37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
-    <col min="3" max="3" width="0.33203125" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="0.109375" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" customWidth="1"/>
-    <col min="13" max="13" width="12" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="0.109375" customWidth="1"/>
-    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="0.28515625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="11" width="12.42578125" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" customWidth="1"/>
+    <col min="16" max="16" width="0.140625" customWidth="1"/>
+    <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="213"/>
-      <c r="E1" s="213"/>
-      <c r="F1" s="213"/>
-      <c r="G1" s="213"/>
-      <c r="H1" s="213"/>
-      <c r="I1" s="213"/>
-      <c r="J1" s="213"/>
-      <c r="K1" s="213"/>
-      <c r="L1" s="213"/>
-      <c r="M1" s="6"/>
+      <c r="D1" s="193"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
+      <c r="G1" s="193"/>
+      <c r="H1" s="193"/>
+      <c r="I1" s="193"/>
+      <c r="J1" s="193"/>
+      <c r="K1" s="193"/>
+      <c r="L1" s="193"/>
+      <c r="M1" s="193"/>
       <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O1" s="6"/>
+    </row>
+    <row r="2" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3023,7 +3084,7 @@
         <v>82</v>
       </c>
       <c r="E2" s="6"/>
-      <c r="F2" s="160">
+      <c r="F2" s="159">
         <v>86134.56</v>
       </c>
       <c r="G2" s="6"/>
@@ -3033,15 +3094,16 @@
         <v>81</v>
       </c>
       <c r="K2" s="6"/>
-      <c r="L2" s="130">
-        <f>3962982.6285+(3962982.6285*5%)</f>
-        <v>4161131.7599250004</v>
-      </c>
-      <c r="M2" s="55"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="129">
+        <f>R4-F2</f>
+        <v>4880009.370000001</v>
+      </c>
       <c r="N2" s="55"/>
-      <c r="O2" s="22"/>
-    </row>
-    <row r="3" spans="1:17" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O2" s="55"/>
+      <c r="P2" s="22"/>
+    </row>
+    <row r="3" spans="1:18" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3053,81 +3115,86 @@
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
-      <c r="L3" s="56"/>
+      <c r="L3" s="6"/>
       <c r="M3" s="56"/>
-      <c r="N3" s="60"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="208" t="s">
+      <c r="N3" s="56"/>
+      <c r="O3" s="60"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="198" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="208" t="s">
+      <c r="B4" s="198" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="208" t="s">
+      <c r="C4" s="198" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="208" t="s">
+      <c r="D4" s="198" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="214" t="s">
+      <c r="E4" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="208" t="s">
+      <c r="F4" s="198" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="218" t="s">
+      <c r="G4" s="200" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="214" t="s">
+      <c r="H4" s="194" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="214" t="s">
+      <c r="I4" s="194" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="214" t="s">
+      <c r="J4" s="194" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="221" t="s">
+      <c r="K4" s="194" t="s">
+        <v>131</v>
+      </c>
+      <c r="L4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="63" t="s">
+      <c r="M4" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="216" t="s">
+      <c r="N4" s="196" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="211" t="s">
+      <c r="O4" s="191" t="s">
         <v>36</v>
       </c>
-      <c r="Q4" s="130">
-        <v>3774269.17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="210"/>
-      <c r="B5" s="210"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="210"/>
-      <c r="E5" s="215"/>
-      <c r="F5" s="210"/>
-      <c r="G5" s="219"/>
-      <c r="H5" s="215"/>
-      <c r="I5" s="220"/>
-      <c r="J5" s="215"/>
-      <c r="K5" s="222"/>
-      <c r="L5" s="61" t="str">
+      <c r="R4" s="129">
+        <v>4966143.9300000006</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="199"/>
+      <c r="B5" s="199"/>
+      <c r="C5" s="205"/>
+      <c r="D5" s="199"/>
+      <c r="E5" s="195"/>
+      <c r="F5" s="199"/>
+      <c r="G5" s="201"/>
+      <c r="H5" s="195"/>
+      <c r="I5" s="202"/>
+      <c r="J5" s="195"/>
+      <c r="K5" s="195"/>
+      <c r="L5" s="204"/>
+      <c r="M5" s="61" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/07</v>
       </c>
-      <c r="M5" s="217"/>
-      <c r="N5" s="212"/>
-    </row>
-    <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="64">
+      <c r="N5" s="197"/>
+      <c r="O5" s="192"/>
+    </row>
+    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="163">
         <v>1</v>
       </c>
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="163" t="s">
         <v>56</v>
       </c>
       <c r="C6" s="64"/>
@@ -3135,11 +3202,11 @@
         <v>6.69</v>
       </c>
       <c r="E6" s="74">
-        <v>270886.01</v>
-      </c>
-      <c r="F6" s="75">
+        <v>284142.01</v>
+      </c>
+      <c r="F6" s="213">
         <f t="shared" ref="F6" si="0">E6</f>
-        <v>270886.01</v>
+        <v>284142.01</v>
       </c>
       <c r="G6" s="76">
         <f t="shared" ref="G6:G23" si="1">E6-F6</f>
@@ -3153,35 +3220,36 @@
         <v>0</v>
       </c>
       <c r="J6" s="78">
-        <f>L$2*D6/100</f>
-        <v>278379.71473898255</v>
-      </c>
-      <c r="K6" s="161">
-        <f t="shared" ref="K6:K23" si="2">F$2*D6/100</f>
+        <f>M$2*D6/100</f>
+        <v>326472.62685300008</v>
+      </c>
+      <c r="K6" s="160"/>
+      <c r="L6" s="160">
+        <f t="shared" ref="L6:L23" si="2">F$2*D6/100</f>
         <v>5762.4020639999999</v>
       </c>
-      <c r="L6" s="80">
-        <f>ROUND(SUM(G6:K6),0) + O6</f>
-        <v>284142.01</v>
-      </c>
-      <c r="M6" s="81">
-        <f>ROUND(L6*6% + L6,0) + O6</f>
-        <v>301191.01</v>
-      </c>
-      <c r="N6" s="82">
-        <f>ROUND(L6*3%,0) + L6</f>
-        <v>292666.01</v>
-      </c>
-      <c r="O6" s="43">
+      <c r="M6" s="80">
+        <f>ROUND(SUM(G6:L6),0) + P6</f>
+        <v>332235.01</v>
+      </c>
+      <c r="N6" s="81">
+        <f>ROUND(M6*6% + M6,0) + P6</f>
+        <v>352169.01</v>
+      </c>
+      <c r="O6" s="82">
+        <f>ROUND(M6*3%,0) + M6</f>
+        <v>342202.01</v>
+      </c>
+      <c r="P6" s="43">
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="64">
+    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="163">
         <f>A6+1</f>
         <v>2</v>
       </c>
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="163" t="s">
         <v>57</v>
       </c>
       <c r="C7" s="65"/>
@@ -3189,107 +3257,111 @@
         <v>5.88</v>
       </c>
       <c r="E7" s="74">
-        <v>1638514.02</v>
-      </c>
-      <c r="F7" s="75"/>
+        <v>1937409.02</v>
+      </c>
+      <c r="F7" s="213"/>
       <c r="G7" s="76">
         <f t="shared" si="1"/>
-        <v>1638514.02</v>
+        <v>1937409.02</v>
       </c>
       <c r="H7" s="76">
         <f t="shared" ref="H7:H23" si="3">IF(G7&gt;0,G7*3%,0)</f>
-        <v>49155.420599999998</v>
+        <v>58122.270599999996</v>
       </c>
       <c r="I7" s="77">
         <v>0</v>
       </c>
       <c r="J7" s="78">
-        <f t="shared" ref="J7:J23" si="4">L$2*D7%</f>
-        <v>244674.54748359002</v>
-      </c>
-      <c r="K7" s="161">
+        <f t="shared" ref="J7:J23" si="4">M$2*D7%</f>
+        <v>286944.55095600005</v>
+      </c>
+      <c r="K7" s="160">
+        <f>24000+99500</f>
+        <v>123500</v>
+      </c>
+      <c r="L7" s="160">
         <f t="shared" si="2"/>
         <v>5064.7121280000001</v>
       </c>
-      <c r="L7" s="80">
-        <f t="shared" ref="L7:L23" si="5">ROUND(SUM(G7:K7),0) + O7</f>
-        <v>1937409.02</v>
-      </c>
-      <c r="M7" s="81">
-        <f t="shared" ref="M7:M23" si="6">ROUND(L7*6% + L7,0) + O7</f>
-        <v>2053654.02</v>
-      </c>
-      <c r="N7" s="82">
-        <f t="shared" ref="N7:N23" si="7">ROUND(L7*3%,0) + L7</f>
-        <v>1995531.02</v>
-      </c>
-      <c r="O7" s="43">
-        <f>O6+0.01</f>
+      <c r="M7" s="80">
+        <f t="shared" ref="M7:M23" si="5">ROUND(SUM(G7:L7),0) + P7</f>
+        <v>2411041.02</v>
+      </c>
+      <c r="N7" s="81">
+        <f t="shared" ref="N7:N23" si="6">ROUND(M7*6% + M7,0) + P7</f>
+        <v>2555703.02</v>
+      </c>
+      <c r="O7" s="82">
+        <f t="shared" ref="O7:O23" si="7">ROUND(M7*3%,0) + M7</f>
+        <v>2483372.02</v>
+      </c>
+      <c r="P7" s="43">
+        <f>P6+0.01</f>
         <v>0.02</v>
       </c>
-      <c r="P7" s="43"/>
-    </row>
-    <row r="8" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="164">
+      <c r="Q7" s="43"/>
+    </row>
+    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="163">
         <f t="shared" ref="A8:A23" si="8">A7+1</f>
         <v>3</v>
       </c>
-      <c r="B8" s="164" t="s">
+      <c r="B8" s="163" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="165"/>
-      <c r="D8" s="166">
+      <c r="C8" s="164"/>
+      <c r="D8" s="165">
         <v>6.65</v>
       </c>
       <c r="E8" s="75">
-        <v>142566.03</v>
-      </c>
-      <c r="F8" s="75">
-        <f>E8+4</f>
-        <v>142570.03</v>
+        <v>290912.03000000003</v>
+      </c>
+      <c r="F8" s="213">
+        <v>200000.03</v>
       </c>
       <c r="G8" s="76">
         <f t="shared" si="1"/>
-        <v>-4</v>
+        <v>90912.000000000029</v>
       </c>
       <c r="H8" s="76">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2727.3600000000006</v>
       </c>
       <c r="I8" s="77">
         <v>0</v>
       </c>
       <c r="J8" s="78">
         <f t="shared" si="4"/>
-        <v>276715.26203501254</v>
-      </c>
-      <c r="K8" s="161">
+        <v>324520.62310500006</v>
+      </c>
+      <c r="K8" s="160"/>
+      <c r="L8" s="160">
         <f t="shared" si="2"/>
         <v>5727.9482400000006</v>
       </c>
-      <c r="L8" s="80">
+      <c r="M8" s="80">
         <f t="shared" si="5"/>
-        <v>282439.03000000003</v>
-      </c>
-      <c r="M8" s="81">
+        <v>423888.03</v>
+      </c>
+      <c r="N8" s="81">
         <f t="shared" si="6"/>
-        <v>299385.03000000003</v>
-      </c>
-      <c r="N8" s="82">
+        <v>449321.03</v>
+      </c>
+      <c r="O8" s="82">
         <f t="shared" si="7"/>
-        <v>290912.03000000003</v>
-      </c>
-      <c r="O8" s="43">
-        <f t="shared" ref="O8:O24" si="9">O7+0.01</f>
+        <v>436605.03</v>
+      </c>
+      <c r="P8" s="43">
+        <f t="shared" ref="P8:P24" si="9">P7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="64">
+    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="163">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="B9" s="64" t="s">
+      <c r="B9" s="163" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="65"/>
@@ -3297,11 +3369,11 @@
         <v>6.73</v>
       </c>
       <c r="E9" s="74">
-        <v>272506.03999999998</v>
-      </c>
-      <c r="F9" s="75">
+        <v>285841.03999999998</v>
+      </c>
+      <c r="F9" s="213">
         <f t="shared" ref="F9:F23" si="10">E9</f>
-        <v>272506.03999999998</v>
+        <v>285841.03999999998</v>
       </c>
       <c r="G9" s="76">
         <f t="shared" si="1"/>
@@ -3316,36 +3388,37 @@
       </c>
       <c r="J9" s="78">
         <f t="shared" si="4"/>
-        <v>280044.16744295252</v>
-      </c>
-      <c r="K9" s="161">
+        <v>328424.63060100004</v>
+      </c>
+      <c r="K9" s="160"/>
+      <c r="L9" s="160">
         <f t="shared" si="2"/>
         <v>5796.855888</v>
       </c>
-      <c r="L9" s="80">
+      <c r="M9" s="80">
         <f t="shared" si="5"/>
-        <v>285841.03999999998</v>
-      </c>
-      <c r="M9" s="81">
+        <v>334221.03999999998</v>
+      </c>
+      <c r="N9" s="81">
         <f t="shared" si="6"/>
-        <v>302992.03999999998</v>
-      </c>
-      <c r="N9" s="82">
+        <v>354274.04</v>
+      </c>
+      <c r="O9" s="82">
         <f t="shared" si="7"/>
-        <v>294416.03999999998</v>
-      </c>
-      <c r="O9" s="43">
+        <v>344248.04</v>
+      </c>
+      <c r="P9" s="43">
         <f t="shared" si="9"/>
         <v>0.04</v>
       </c>
-      <c r="Q9" s="43"/>
-    </row>
-    <row r="10" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="188">
+      <c r="R9" s="43"/>
+    </row>
+    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="163">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="B10" s="188" t="s">
+      <c r="B10" s="163" t="s">
         <v>60</v>
       </c>
       <c r="C10" s="65"/>
@@ -3353,11 +3426,11 @@
         <v>8.0399999999999991</v>
       </c>
       <c r="E10" s="74">
-        <v>335369.05</v>
-      </c>
-      <c r="F10" s="75">
-        <f>E10</f>
-        <v>335369.05</v>
+        <v>351724.05</v>
+      </c>
+      <c r="F10" s="213">
+        <f>341480.05+10244</f>
+        <v>351724.05</v>
       </c>
       <c r="G10" s="76">
         <f t="shared" si="1"/>
@@ -3372,39 +3445,40 @@
       </c>
       <c r="J10" s="78">
         <f t="shared" si="4"/>
-        <v>334554.99349796999</v>
-      </c>
-      <c r="K10" s="161">
+        <v>392352.753348</v>
+      </c>
+      <c r="K10" s="160"/>
+      <c r="L10" s="160">
         <f t="shared" si="2"/>
         <v>6925.2186239999983</v>
       </c>
-      <c r="L10" s="80">
+      <c r="M10" s="80">
         <f t="shared" si="5"/>
-        <v>341480.05</v>
-      </c>
-      <c r="M10" s="81">
+        <v>399278.05</v>
+      </c>
+      <c r="N10" s="81">
         <f t="shared" si="6"/>
-        <v>361969.05</v>
-      </c>
-      <c r="N10" s="82">
+        <v>423235.05</v>
+      </c>
+      <c r="O10" s="82">
         <f t="shared" si="7"/>
-        <v>351724.05</v>
-      </c>
-      <c r="O10" s="43">
+        <v>411256.05</v>
+      </c>
+      <c r="P10" s="43">
         <f t="shared" si="9"/>
         <v>0.05</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>98</v>
       </c>
-      <c r="Q10" s="43"/>
-    </row>
-    <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="188">
+      <c r="R10" s="43"/>
+    </row>
+    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="163">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="B11" s="188" t="s">
+      <c r="B11" s="163" t="s">
         <v>61</v>
       </c>
       <c r="C11" s="64"/>
@@ -3412,11 +3486,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="E11" s="74">
-        <v>197269.06</v>
-      </c>
-      <c r="F11" s="75">
+        <v>200896.06</v>
+      </c>
+      <c r="F11" s="213">
         <f>E11</f>
-        <v>197269.06</v>
+        <v>200896.06</v>
       </c>
       <c r="G11" s="76">
         <f t="shared" si="1"/>
@@ -3431,87 +3505,91 @@
       </c>
       <c r="J11" s="78">
         <f t="shared" si="4"/>
-        <v>196821.53224445254</v>
-      </c>
-      <c r="K11" s="161">
+        <v>230824.44320100005</v>
+      </c>
+      <c r="K11" s="160"/>
+      <c r="L11" s="160">
         <f t="shared" si="2"/>
         <v>4074.1646880000003</v>
       </c>
-      <c r="L11" s="80">
+      <c r="M11" s="80">
         <f t="shared" si="5"/>
-        <v>200896.06</v>
-      </c>
-      <c r="M11" s="81">
+        <v>234899.06</v>
+      </c>
+      <c r="N11" s="81">
         <f t="shared" si="6"/>
-        <v>212950.06</v>
-      </c>
-      <c r="N11" s="82">
+        <v>248993.06</v>
+      </c>
+      <c r="O11" s="82">
         <f t="shared" si="7"/>
-        <v>206923.06</v>
-      </c>
-      <c r="O11" s="43">
+        <v>241946.06</v>
+      </c>
+      <c r="P11" s="43">
         <f t="shared" si="9"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="164">
+    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="214">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="B12" s="164" t="s">
+      <c r="B12" s="214" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="64"/>
-      <c r="D12" s="73">
+      <c r="C12" s="214"/>
+      <c r="D12" s="215">
         <v>5.67</v>
       </c>
-      <c r="E12" s="74">
-        <v>729893.07</v>
-      </c>
-      <c r="F12" s="75"/>
-      <c r="G12" s="76">
+      <c r="E12" s="216">
+        <v>992610.07</v>
+      </c>
+      <c r="F12" s="217">
+        <v>300000</v>
+      </c>
+      <c r="G12" s="218">
         <f t="shared" si="1"/>
-        <v>729893.07</v>
-      </c>
-      <c r="H12" s="76">
+        <v>692610.07</v>
+      </c>
+      <c r="H12" s="218">
         <f t="shared" si="3"/>
-        <v>21896.792099999999</v>
-      </c>
-      <c r="I12" s="77">
-        <v>0</v>
-      </c>
-      <c r="J12" s="78">
+        <v>20778.302099999997</v>
+      </c>
+      <c r="I12" s="217">
+        <v>0</v>
+      </c>
+      <c r="J12" s="219">
         <f t="shared" si="4"/>
-        <v>235936.17078774751</v>
-      </c>
-      <c r="K12" s="161">
+        <v>276696.53127900005</v>
+      </c>
+      <c r="K12" s="220"/>
+      <c r="L12" s="220">
         <f t="shared" si="2"/>
         <v>4883.8295519999992</v>
       </c>
-      <c r="L12" s="80">
+      <c r="M12" s="221">
         <f t="shared" si="5"/>
-        <v>992610.07</v>
-      </c>
-      <c r="M12" s="81">
+        <v>994969.07</v>
+      </c>
+      <c r="N12" s="222">
         <f t="shared" si="6"/>
-        <v>1052167.07</v>
-      </c>
-      <c r="N12" s="82">
+        <v>1054667.07</v>
+      </c>
+      <c r="O12" s="223">
         <f t="shared" si="7"/>
-        <v>1022388.07</v>
-      </c>
-      <c r="O12" s="43">
+        <v>1024818.07</v>
+      </c>
+      <c r="P12" s="43">
         <f t="shared" si="9"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="64">
+    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="163">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="B13" s="64" t="s">
+      <c r="B13" s="163" t="s">
         <v>63</v>
       </c>
       <c r="C13" s="65"/>
@@ -3519,11 +3597,11 @@
         <v>5.67</v>
       </c>
       <c r="E13" s="74">
-        <v>236472.08</v>
-      </c>
-      <c r="F13" s="75">
+        <v>240820.08</v>
+      </c>
+      <c r="F13" s="213">
         <f>E13</f>
-        <v>236472.08</v>
+        <v>240820.08</v>
       </c>
       <c r="G13" s="76">
         <f t="shared" si="1"/>
@@ -3538,38 +3616,39 @@
       </c>
       <c r="J13" s="78">
         <f t="shared" si="4"/>
-        <v>235936.17078774751</v>
-      </c>
-      <c r="K13" s="161">
+        <v>276696.53127900005</v>
+      </c>
+      <c r="K13" s="160"/>
+      <c r="L13" s="160">
         <f t="shared" si="2"/>
         <v>4883.8295519999992</v>
       </c>
-      <c r="L13" s="80">
+      <c r="M13" s="80">
         <f t="shared" si="5"/>
-        <v>240820.08</v>
-      </c>
-      <c r="M13" s="81">
+        <v>281580.08</v>
+      </c>
+      <c r="N13" s="81">
         <f t="shared" si="6"/>
-        <v>255269.08</v>
-      </c>
-      <c r="N13" s="82">
+        <v>298475.08</v>
+      </c>
+      <c r="O13" s="82">
         <f t="shared" si="7"/>
-        <v>248045.08</v>
-      </c>
-      <c r="O13" s="43">
+        <v>290027.08</v>
+      </c>
+      <c r="P13" s="43">
         <f t="shared" si="9"/>
         <v>0.08</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="64">
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="163">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="B14" s="64" t="s">
+      <c r="B14" s="163" t="s">
         <v>64</v>
       </c>
       <c r="C14" s="65"/>
@@ -3577,11 +3656,11 @@
         <v>7.67</v>
       </c>
       <c r="E14" s="74">
-        <v>310567.09000000003</v>
-      </c>
-      <c r="F14" s="75">
+        <v>325765.09000000003</v>
+      </c>
+      <c r="F14" s="213">
         <f t="shared" si="10"/>
-        <v>310567.09000000003</v>
+        <v>325765.09000000003</v>
       </c>
       <c r="G14" s="76">
         <f t="shared" si="1"/>
@@ -3596,35 +3675,36 @@
       </c>
       <c r="J14" s="78">
         <f t="shared" si="4"/>
-        <v>319158.80598624755</v>
-      </c>
-      <c r="K14" s="161">
+        <v>374296.7186790001</v>
+      </c>
+      <c r="K14" s="160"/>
+      <c r="L14" s="160">
         <f t="shared" si="2"/>
         <v>6606.5207519999994</v>
       </c>
-      <c r="L14" s="80">
+      <c r="M14" s="80">
         <f t="shared" si="5"/>
-        <v>325765.09000000003</v>
-      </c>
-      <c r="M14" s="81">
+        <v>380903.09</v>
+      </c>
+      <c r="N14" s="81">
         <f t="shared" si="6"/>
-        <v>345311.09</v>
-      </c>
-      <c r="N14" s="82">
+        <v>403757.09</v>
+      </c>
+      <c r="O14" s="82">
         <f t="shared" si="7"/>
-        <v>335538.09000000003</v>
-      </c>
-      <c r="O14" s="43">
+        <v>392330.09</v>
+      </c>
+      <c r="P14" s="43">
         <f t="shared" si="9"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="64">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="163">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="B15" s="64" t="s">
+      <c r="B15" s="163" t="s">
         <v>65</v>
       </c>
       <c r="C15" s="65"/>
@@ -3632,11 +3712,11 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="E15" s="74">
-        <v>55047.1</v>
-      </c>
-      <c r="F15" s="75">
+        <v>208116.1</v>
+      </c>
+      <c r="F15" s="213">
         <f>E15</f>
-        <v>55047.1</v>
+        <v>208116.1</v>
       </c>
       <c r="G15" s="76">
         <f t="shared" si="1"/>
@@ -3651,35 +3731,36 @@
       </c>
       <c r="J15" s="78">
         <f t="shared" si="4"/>
-        <v>203895.45623632503</v>
-      </c>
-      <c r="K15" s="161">
+        <v>239120.45913000006</v>
+      </c>
+      <c r="K15" s="160"/>
+      <c r="L15" s="160">
         <f t="shared" si="2"/>
         <v>4220.5934400000006</v>
       </c>
-      <c r="L15" s="80">
+      <c r="M15" s="80">
         <f t="shared" si="5"/>
-        <v>208116.1</v>
-      </c>
-      <c r="M15" s="81">
+        <v>243341.1</v>
+      </c>
+      <c r="N15" s="81">
         <f t="shared" si="6"/>
-        <v>220603.1</v>
-      </c>
-      <c r="N15" s="82">
+        <v>257942.1</v>
+      </c>
+      <c r="O15" s="82">
         <f t="shared" si="7"/>
-        <v>214359.1</v>
-      </c>
-      <c r="O15" s="43">
+        <v>250641.1</v>
+      </c>
+      <c r="P15" s="43">
         <f t="shared" si="9"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="64">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="163">
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="B16" s="64" t="s">
+      <c r="B16" s="163" t="s">
         <v>66</v>
       </c>
       <c r="C16" s="65"/>
@@ -3687,11 +3768,11 @@
         <v>5.63</v>
       </c>
       <c r="E16" s="74">
-        <v>227965.11</v>
-      </c>
-      <c r="F16" s="75">
+        <v>239121.11</v>
+      </c>
+      <c r="F16" s="213">
         <f t="shared" si="10"/>
-        <v>227965.11</v>
+        <v>239121.11</v>
       </c>
       <c r="G16" s="76">
         <f t="shared" si="1"/>
@@ -3706,35 +3787,36 @@
       </c>
       <c r="J16" s="78">
         <f t="shared" si="4"/>
-        <v>234271.71808377749</v>
-      </c>
-      <c r="K16" s="161">
+        <v>274744.52753100003</v>
+      </c>
+      <c r="K16" s="160"/>
+      <c r="L16" s="160">
         <f t="shared" si="2"/>
         <v>4849.375728</v>
       </c>
-      <c r="L16" s="80">
+      <c r="M16" s="80">
         <f t="shared" si="5"/>
-        <v>239121.11</v>
-      </c>
-      <c r="M16" s="81">
+        <v>279594.11</v>
+      </c>
+      <c r="N16" s="81">
         <f t="shared" si="6"/>
-        <v>253468.11</v>
-      </c>
-      <c r="N16" s="82">
+        <v>296370.11</v>
+      </c>
+      <c r="O16" s="82">
         <f t="shared" si="7"/>
-        <v>246295.11</v>
-      </c>
-      <c r="O16" s="43">
+        <v>287982.11</v>
+      </c>
+      <c r="P16" s="43">
         <f t="shared" si="9"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="64">
+    <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="163">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="B17" s="64" t="s">
+      <c r="B17" s="163" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="65"/>
@@ -3742,11 +3824,11 @@
         <v>5.55</v>
       </c>
       <c r="E17" s="74">
-        <v>224726.12</v>
-      </c>
-      <c r="F17" s="75">
-        <f t="shared" si="10"/>
-        <v>224726.12</v>
+        <v>235723.12</v>
+      </c>
+      <c r="F17" s="213">
+        <f>E17</f>
+        <v>235723.12</v>
       </c>
       <c r="G17" s="76">
         <f t="shared" si="1"/>
@@ -3761,35 +3843,36 @@
       </c>
       <c r="J17" s="78">
         <f t="shared" si="4"/>
-        <v>230942.81267583751</v>
-      </c>
-      <c r="K17" s="161">
+        <v>270840.52003500005</v>
+      </c>
+      <c r="K17" s="160"/>
+      <c r="L17" s="160">
         <f t="shared" si="2"/>
         <v>4780.4680799999996</v>
       </c>
-      <c r="L17" s="80">
+      <c r="M17" s="80">
         <f t="shared" si="5"/>
-        <v>235723.12</v>
-      </c>
-      <c r="M17" s="81">
+        <v>275621.12</v>
+      </c>
+      <c r="N17" s="81">
         <f t="shared" si="6"/>
-        <v>249867.12</v>
-      </c>
-      <c r="N17" s="82">
+        <v>292158.12</v>
+      </c>
+      <c r="O17" s="82">
         <f t="shared" si="7"/>
-        <v>242795.12</v>
-      </c>
-      <c r="O17" s="43">
+        <v>283890.12</v>
+      </c>
+      <c r="P17" s="43">
         <f t="shared" si="9"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="64">
+    <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="163">
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
-      <c r="B18" s="64" t="s">
+      <c r="B18" s="163" t="s">
         <v>68</v>
       </c>
       <c r="C18" s="65"/>
@@ -3797,11 +3880,11 @@
         <v>11.06</v>
       </c>
       <c r="E18" s="74">
-        <v>447832.13</v>
-      </c>
-      <c r="F18" s="75">
+        <v>469748.13</v>
+      </c>
+      <c r="F18" s="213">
         <f t="shared" si="10"/>
-        <v>447832.13</v>
+        <v>469748.13</v>
       </c>
       <c r="G18" s="76">
         <f t="shared" si="1"/>
@@ -3816,35 +3899,36 @@
       </c>
       <c r="J18" s="78">
         <f t="shared" si="4"/>
-        <v>460221.17264770507</v>
-      </c>
-      <c r="K18" s="161">
+        <v>539729.03632200009</v>
+      </c>
+      <c r="K18" s="160"/>
+      <c r="L18" s="160">
         <f t="shared" si="2"/>
         <v>9526.4823360000009</v>
       </c>
-      <c r="L18" s="80">
+      <c r="M18" s="80">
         <f t="shared" si="5"/>
-        <v>469748.13</v>
-      </c>
-      <c r="M18" s="81">
+        <v>549256.13</v>
+      </c>
+      <c r="N18" s="81">
         <f t="shared" si="6"/>
-        <v>497933.13</v>
-      </c>
-      <c r="N18" s="82">
+        <v>582211.13</v>
+      </c>
+      <c r="O18" s="82">
         <f t="shared" si="7"/>
-        <v>483840.13</v>
-      </c>
-      <c r="O18" s="43">
+        <v>565734.13</v>
+      </c>
+      <c r="P18" s="43">
         <f t="shared" si="9"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="193">
+    <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="163">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="B19" s="193" t="s">
+      <c r="B19" s="163" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="65"/>
@@ -3852,69 +3936,70 @@
         <v>3.3</v>
       </c>
       <c r="E19" s="74">
-        <v>208649.14</v>
-      </c>
-      <c r="F19" s="75">
-        <f>130778+72843</f>
-        <v>203621</v>
+        <v>145339.14000000001</v>
+      </c>
+      <c r="F19" s="213">
+        <f>137317.14+2842.14+5180</f>
+        <v>145339.28000000003</v>
       </c>
       <c r="G19" s="76">
         <f t="shared" si="1"/>
-        <v>5028.140000000014</v>
+        <v>-0.14000000001396984</v>
       </c>
       <c r="H19" s="76">
         <f t="shared" si="3"/>
-        <v>150.84420000000043</v>
+        <v>0</v>
       </c>
       <c r="I19" s="77">
         <v>0</v>
       </c>
       <c r="J19" s="78">
         <f t="shared" si="4"/>
-        <v>137317.34807752501</v>
-      </c>
-      <c r="K19" s="161">
+        <v>161040.30921000004</v>
+      </c>
+      <c r="K19" s="160"/>
+      <c r="L19" s="160">
         <f t="shared" si="2"/>
         <v>2842.4404799999993</v>
       </c>
-      <c r="L19" s="80">
+      <c r="M19" s="80">
         <f t="shared" si="5"/>
-        <v>145339.14000000001</v>
-      </c>
-      <c r="M19" s="81">
+        <v>163883.14000000001</v>
+      </c>
+      <c r="N19" s="81">
         <f t="shared" si="6"/>
-        <v>154059.14000000001</v>
-      </c>
-      <c r="N19" s="82">
+        <v>173716.14</v>
+      </c>
+      <c r="O19" s="82">
         <f t="shared" si="7"/>
-        <v>149699.14000000001</v>
-      </c>
-      <c r="O19" s="43">
+        <v>168799.14</v>
+      </c>
+      <c r="P19" s="43">
         <f t="shared" si="9"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="P19" t="s">
+      <c r="Q19" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="164">
+    <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="163">
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="B20" s="164" t="s">
+      <c r="B20" s="163" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="165"/>
-      <c r="D20" s="166">
+      <c r="C20" s="164"/>
+      <c r="D20" s="165">
         <v>1.8</v>
       </c>
       <c r="E20" s="75">
-        <v>72884.149999999994</v>
-      </c>
-      <c r="F20" s="75">
+        <v>76451.149999999994</v>
+      </c>
+      <c r="F20" s="213">
         <f>E20</f>
-        <v>72884.149999999994</v>
+        <v>76451.149999999994</v>
       </c>
       <c r="G20" s="76">
         <f t="shared" si="1"/>
@@ -3929,33 +4014,34 @@
       </c>
       <c r="J20" s="78">
         <f t="shared" si="4"/>
-        <v>74900.371678650015</v>
-      </c>
-      <c r="K20" s="161">
+        <v>87840.168660000025</v>
+      </c>
+      <c r="K20" s="160"/>
+      <c r="L20" s="160">
         <f t="shared" si="2"/>
         <v>1550.4220800000001</v>
       </c>
-      <c r="L20" s="80">
+      <c r="M20" s="80">
         <f t="shared" si="5"/>
-        <v>76451.149999999994</v>
-      </c>
-      <c r="M20" s="81">
+        <v>89391.15</v>
+      </c>
+      <c r="N20" s="81">
         <f t="shared" si="6"/>
-        <v>81038.149999999994</v>
-      </c>
-      <c r="N20" s="82">
+        <v>94755.15</v>
+      </c>
+      <c r="O20" s="82">
         <f t="shared" si="7"/>
-        <v>78745.149999999994</v>
-      </c>
-      <c r="O20" s="43">
+        <v>92073.15</v>
+      </c>
+      <c r="P20" s="43">
         <f t="shared" si="9"/>
         <v>0.15</v>
       </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="64">
         <f t="shared" si="8"/>
         <v>16</v>
@@ -3968,11 +4054,11 @@
         <v>3.22</v>
       </c>
       <c r="E21" s="74">
-        <v>130382.16</v>
-      </c>
-      <c r="F21" s="75">
+        <v>136762.16</v>
+      </c>
+      <c r="F21" s="213">
         <f t="shared" si="10"/>
-        <v>130382.16</v>
+        <v>136762.16</v>
       </c>
       <c r="G21" s="76">
         <f t="shared" si="1"/>
@@ -3987,35 +4073,36 @@
       </c>
       <c r="J21" s="78">
         <f t="shared" si="4"/>
-        <v>133988.442669585</v>
-      </c>
-      <c r="K21" s="161">
+        <v>157136.30171400003</v>
+      </c>
+      <c r="K21" s="160"/>
+      <c r="L21" s="160">
         <f t="shared" si="2"/>
         <v>2773.5328319999999</v>
       </c>
-      <c r="L21" s="80">
+      <c r="M21" s="80">
         <f t="shared" si="5"/>
-        <v>136762.16</v>
-      </c>
-      <c r="M21" s="81">
+        <v>159910.16</v>
+      </c>
+      <c r="N21" s="81">
         <f t="shared" si="6"/>
-        <v>144968.16</v>
-      </c>
-      <c r="N21" s="82">
+        <v>169505.16</v>
+      </c>
+      <c r="O21" s="82">
         <f t="shared" si="7"/>
-        <v>140865.16</v>
-      </c>
-      <c r="O21" s="43">
+        <v>164707.16</v>
+      </c>
+      <c r="P21" s="43">
         <f t="shared" si="9"/>
         <v>0.16</v>
       </c>
-      <c r="P21" s="124"/>
-      <c r="Q21" s="168"/>
-      <c r="R21" s="168"/>
-      <c r="S21" s="168"/>
-      <c r="T21" s="168"/>
-    </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q21" s="123"/>
+      <c r="R21" s="167"/>
+      <c r="S21" s="167"/>
+      <c r="T21" s="167"/>
+      <c r="U21" s="167"/>
+    </row>
+    <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="64">
         <f t="shared" si="8"/>
         <v>17</v>
@@ -4028,55 +4115,56 @@
         <v>2.61</v>
       </c>
       <c r="E22" s="75">
-        <v>472462.17</v>
-      </c>
-      <c r="F22" s="75">
-        <v>350000</v>
+        <v>236990.17</v>
+      </c>
+      <c r="F22" s="213">
+        <v>0</v>
       </c>
       <c r="G22" s="76">
         <f t="shared" si="1"/>
-        <v>122462.16999999998</v>
+        <v>236990.17</v>
       </c>
       <c r="H22" s="76">
         <f t="shared" si="3"/>
-        <v>3673.8650999999995</v>
+        <v>7109.7051000000001</v>
       </c>
       <c r="I22" s="77">
         <v>0</v>
       </c>
       <c r="J22" s="78">
         <f t="shared" si="4"/>
-        <v>108605.5389340425</v>
-      </c>
-      <c r="K22" s="161">
+        <v>127368.24455700001</v>
+      </c>
+      <c r="K22" s="160"/>
+      <c r="L22" s="160">
         <f t="shared" si="2"/>
         <v>2248.1120159999996</v>
       </c>
-      <c r="L22" s="80">
+      <c r="M22" s="80">
         <f t="shared" si="5"/>
-        <v>236990.17</v>
-      </c>
-      <c r="M22" s="81">
+        <v>373716.17</v>
+      </c>
+      <c r="N22" s="81">
         <f t="shared" si="6"/>
-        <v>251210.17</v>
-      </c>
-      <c r="N22" s="82">
+        <v>396139.17</v>
+      </c>
+      <c r="O22" s="82">
         <f t="shared" si="7"/>
-        <v>244100.17</v>
-      </c>
-      <c r="O22" s="43">
+        <v>384927.17</v>
+      </c>
+      <c r="P22" s="43">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
-      <c r="P22" s="124" t="s">
+      <c r="Q22" s="123" t="s">
         <v>99</v>
       </c>
-      <c r="Q22" s="168"/>
-      <c r="R22" s="168"/>
-      <c r="S22" s="168"/>
-      <c r="T22" s="168"/>
-    </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R22" s="167"/>
+      <c r="S22" s="167"/>
+      <c r="T22" s="167"/>
+      <c r="U22" s="167"/>
+    </row>
+    <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="64">
         <f t="shared" si="8"/>
         <v>18</v>
@@ -4084,16 +4172,16 @@
       <c r="B23" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="129"/>
+      <c r="C23" s="128"/>
       <c r="D23" s="73">
         <v>4.28</v>
       </c>
       <c r="E23" s="74">
-        <v>173302.18</v>
-      </c>
-      <c r="F23" s="75">
+        <v>181783.18</v>
+      </c>
+      <c r="F23" s="213">
         <f t="shared" si="10"/>
-        <v>173302.18</v>
+        <v>181783.18</v>
       </c>
       <c r="G23" s="76">
         <f t="shared" si="1"/>
@@ -4108,55 +4196,57 @@
       </c>
       <c r="J23" s="78">
         <f t="shared" si="4"/>
-        <v>178096.43932479003</v>
-      </c>
-      <c r="K23" s="161">
+        <v>208864.40103600005</v>
+      </c>
+      <c r="K23" s="160"/>
+      <c r="L23" s="160">
         <f t="shared" si="2"/>
         <v>3686.5591680000002</v>
       </c>
-      <c r="L23" s="80">
+      <c r="M23" s="80">
         <f t="shared" si="5"/>
-        <v>181783.18</v>
-      </c>
-      <c r="M23" s="81">
+        <v>212551.18</v>
+      </c>
+      <c r="N23" s="81">
         <f t="shared" si="6"/>
-        <v>192690.18</v>
-      </c>
-      <c r="N23" s="82">
+        <v>225304.18</v>
+      </c>
+      <c r="O23" s="82">
         <f t="shared" si="7"/>
-        <v>187236.18</v>
-      </c>
-      <c r="O23" s="43">
+        <v>218928.18</v>
+      </c>
+      <c r="P23" s="43">
         <f t="shared" si="9"/>
         <v>0.18000000000000002</v>
       </c>
-      <c r="P23" s="168"/>
-      <c r="Q23" s="168"/>
-      <c r="R23" s="168"/>
-      <c r="S23" s="168"/>
-      <c r="T23" s="168"/>
-    </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q23" s="167"/>
+      <c r="R23" s="167"/>
+      <c r="S23" s="167"/>
+      <c r="T23" s="167"/>
+      <c r="U23" s="167"/>
+    </row>
+    <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="64"/>
       <c r="B24" s="64"/>
       <c r="C24" s="65"/>
       <c r="D24" s="73"/>
       <c r="E24" s="74"/>
-      <c r="F24" s="167"/>
+      <c r="F24" s="166"/>
       <c r="G24" s="76"/>
       <c r="H24" s="76"/>
       <c r="I24" s="77"/>
       <c r="J24" s="78"/>
-      <c r="K24" s="79"/>
-      <c r="L24" s="80"/>
-      <c r="M24" s="81"/>
-      <c r="N24" s="82"/>
-      <c r="O24" s="43">
+      <c r="K24" s="160"/>
+      <c r="L24" s="79"/>
+      <c r="M24" s="80"/>
+      <c r="N24" s="81"/>
+      <c r="O24" s="82"/>
+      <c r="P24" s="43">
         <f t="shared" si="9"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="83"/>
       <c r="B25" s="64"/>
       <c r="C25" s="65"/>
@@ -4167,13 +4257,14 @@
       <c r="H25" s="76"/>
       <c r="I25" s="77"/>
       <c r="J25" s="88"/>
-      <c r="K25" s="89"/>
-      <c r="L25" s="80"/>
-      <c r="M25" s="81"/>
-      <c r="N25" s="82"/>
-      <c r="O25" s="43"/>
-    </row>
-    <row r="26" spans="1:20" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K25" s="212"/>
+      <c r="L25" s="89"/>
+      <c r="M25" s="80"/>
+      <c r="N25" s="81"/>
+      <c r="O25" s="82"/>
+      <c r="P25" s="43"/>
+    </row>
+    <row r="26" spans="1:21" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="83"/>
       <c r="B26" s="66"/>
       <c r="C26" s="65"/>
@@ -4184,13 +4275,14 @@
       <c r="H26" s="76"/>
       <c r="I26" s="77"/>
       <c r="J26" s="88"/>
-      <c r="K26" s="89"/>
-      <c r="L26" s="80"/>
-      <c r="M26" s="81"/>
-      <c r="N26" s="82"/>
-      <c r="O26" s="43"/>
-    </row>
-    <row r="27" spans="1:20" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K26" s="212"/>
+      <c r="L26" s="89"/>
+      <c r="M26" s="80"/>
+      <c r="N26" s="81"/>
+      <c r="O26" s="82"/>
+      <c r="P26" s="43"/>
+    </row>
+    <row r="27" spans="1:21" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="84"/>
       <c r="B27" s="64"/>
       <c r="C27" s="65"/>
@@ -4201,13 +4293,14 @@
       <c r="H27" s="76"/>
       <c r="I27" s="77"/>
       <c r="J27" s="88"/>
-      <c r="K27" s="89"/>
-      <c r="L27" s="80"/>
-      <c r="M27" s="81"/>
-      <c r="N27" s="82"/>
-      <c r="O27" s="43"/>
-    </row>
-    <row r="28" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K27" s="212"/>
+      <c r="L27" s="89"/>
+      <c r="M27" s="80"/>
+      <c r="N27" s="81"/>
+      <c r="O27" s="82"/>
+      <c r="P27" s="43"/>
+    </row>
+    <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="64"/>
       <c r="B28" s="90"/>
       <c r="C28" s="90"/>
@@ -4218,13 +4311,14 @@
       <c r="H28" s="76"/>
       <c r="I28" s="77"/>
       <c r="J28" s="88"/>
-      <c r="K28" s="89"/>
-      <c r="L28" s="91"/>
-      <c r="M28" s="92"/>
-      <c r="N28" s="93"/>
-      <c r="O28" s="43"/>
-    </row>
-    <row r="29" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K28" s="212"/>
+      <c r="L28" s="89"/>
+      <c r="M28" s="91"/>
+      <c r="N28" s="92"/>
+      <c r="O28" s="93"/>
+      <c r="P28" s="43"/>
+    </row>
+    <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="94"/>
       <c r="B29" s="95"/>
       <c r="C29" s="95"/>
@@ -4234,148 +4328,156 @@
       </c>
       <c r="E29" s="53">
         <f>SUM(E6:E28)</f>
-        <v>6147292.71</v>
+        <v>6840153.71</v>
       </c>
       <c r="F29" s="62">
         <f>SUM(F6:F28)</f>
-        <v>3651399.3100000005</v>
+        <v>3882232.5900000008</v>
       </c>
       <c r="G29" s="62">
         <f>SUM(G6:G28)</f>
-        <v>2495893.4</v>
+        <v>2957921.1199999996</v>
       </c>
       <c r="H29" s="62">
-        <f t="shared" ref="H29:M29" si="11">SUM(H6:H28)</f>
-        <v>74876.922000000006</v>
+        <f t="shared" ref="H29:N29" si="11">SUM(H6:H28)</f>
+        <v>88737.637799999997</v>
       </c>
       <c r="I29" s="62">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J29" s="133">
+      <c r="J29" s="132">
         <f t="shared" si="11"/>
-        <v>4164460.6653329404</v>
-      </c>
-      <c r="K29" s="62">
+        <v>4883913.3774960004</v>
+      </c>
+      <c r="K29" s="132"/>
+      <c r="L29" s="62">
         <f t="shared" si="11"/>
         <v>86203.467647999991</v>
       </c>
-      <c r="L29" s="97">
-        <f>SUM(L6:L23)</f>
-        <v>6821436.71</v>
-      </c>
       <c r="M29" s="97">
+        <f>SUM(M6:M23)</f>
+        <v>8140278.71</v>
+      </c>
+      <c r="N29" s="97">
         <f t="shared" si="11"/>
-        <v>7230725.71</v>
-      </c>
-      <c r="N29" s="97">
-        <f>SUM(N6:N28)</f>
-        <v>7026078.71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>8628695.7100000009</v>
+      </c>
+      <c r="O29" s="97">
+        <f>SUM(O6:O28)</f>
+        <v>8384486.71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="50"/>
       <c r="C30" s="50"/>
     </row>
-    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="198" t="str">
+    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="189" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="198"/>
-      <c r="D32" s="198"/>
-      <c r="E32" s="198"/>
-      <c r="F32" s="198"/>
-      <c r="G32" s="198"/>
-      <c r="H32" s="198"/>
-      <c r="I32" s="198"/>
-      <c r="J32" s="198"/>
-      <c r="K32" s="198"/>
-      <c r="L32" s="198"/>
-    </row>
-    <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="198"/>
-      <c r="C33" s="198"/>
-      <c r="D33" s="198"/>
-      <c r="E33" s="198"/>
-      <c r="F33" s="198"/>
-      <c r="G33" s="198"/>
-      <c r="H33" s="198"/>
-      <c r="I33" s="198"/>
-      <c r="J33" s="198"/>
-      <c r="K33" s="198"/>
-      <c r="L33" s="198"/>
-    </row>
-    <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="198"/>
-      <c r="C34" s="198"/>
-      <c r="D34" s="198"/>
-      <c r="E34" s="198"/>
-      <c r="F34" s="198"/>
-      <c r="G34" s="198"/>
-      <c r="H34" s="198"/>
-      <c r="I34" s="198"/>
-      <c r="J34" s="198"/>
-      <c r="K34" s="198"/>
-      <c r="L34" s="198"/>
-    </row>
-    <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="198"/>
-      <c r="C35" s="198"/>
-      <c r="D35" s="198"/>
-      <c r="E35" s="198"/>
-      <c r="F35" s="198"/>
-      <c r="G35" s="198"/>
-      <c r="H35" s="198"/>
-      <c r="I35" s="198"/>
-      <c r="J35" s="198"/>
-      <c r="K35" s="198"/>
-      <c r="L35" s="198"/>
-    </row>
-    <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="198"/>
-      <c r="C36" s="198"/>
-      <c r="D36" s="198"/>
-      <c r="E36" s="198"/>
-      <c r="F36" s="198"/>
-      <c r="G36" s="198"/>
-      <c r="H36" s="198"/>
-      <c r="I36" s="198"/>
-      <c r="J36" s="198"/>
-      <c r="K36" s="198"/>
-      <c r="L36" s="198"/>
-    </row>
-    <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="198"/>
-      <c r="C37" s="198"/>
-      <c r="D37" s="198"/>
-      <c r="E37" s="198"/>
-      <c r="F37" s="198"/>
-      <c r="G37" s="198"/>
-      <c r="H37" s="198"/>
-      <c r="I37" s="198"/>
-      <c r="J37" s="198"/>
-      <c r="K37" s="198"/>
-      <c r="L37" s="198"/>
+      <c r="C32" s="189"/>
+      <c r="D32" s="189"/>
+      <c r="E32" s="189"/>
+      <c r="F32" s="189"/>
+      <c r="G32" s="189"/>
+      <c r="H32" s="189"/>
+      <c r="I32" s="189"/>
+      <c r="J32" s="189"/>
+      <c r="K32" s="189"/>
+      <c r="L32" s="189"/>
+      <c r="M32" s="189"/>
+    </row>
+    <row r="33" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="189"/>
+      <c r="C33" s="189"/>
+      <c r="D33" s="189"/>
+      <c r="E33" s="189"/>
+      <c r="F33" s="189"/>
+      <c r="G33" s="189"/>
+      <c r="H33" s="189"/>
+      <c r="I33" s="189"/>
+      <c r="J33" s="189"/>
+      <c r="K33" s="189"/>
+      <c r="L33" s="189"/>
+      <c r="M33" s="189"/>
+    </row>
+    <row r="34" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="189"/>
+      <c r="C34" s="189"/>
+      <c r="D34" s="189"/>
+      <c r="E34" s="189"/>
+      <c r="F34" s="189"/>
+      <c r="G34" s="189"/>
+      <c r="H34" s="189"/>
+      <c r="I34" s="189"/>
+      <c r="J34" s="189"/>
+      <c r="K34" s="189"/>
+      <c r="L34" s="189"/>
+      <c r="M34" s="189"/>
+    </row>
+    <row r="35" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="189"/>
+      <c r="C35" s="189"/>
+      <c r="D35" s="189"/>
+      <c r="E35" s="189"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="189"/>
+      <c r="H35" s="189"/>
+      <c r="I35" s="189"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="189"/>
+      <c r="L35" s="189"/>
+      <c r="M35" s="189"/>
+    </row>
+    <row r="36" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="189"/>
+      <c r="C36" s="189"/>
+      <c r="D36" s="189"/>
+      <c r="E36" s="189"/>
+      <c r="F36" s="189"/>
+      <c r="G36" s="189"/>
+      <c r="H36" s="189"/>
+      <c r="I36" s="189"/>
+      <c r="J36" s="189"/>
+      <c r="K36" s="189"/>
+      <c r="L36" s="189"/>
+      <c r="M36" s="189"/>
+    </row>
+    <row r="37" spans="2:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="189"/>
+      <c r="C37" s="189"/>
+      <c r="D37" s="189"/>
+      <c r="E37" s="189"/>
+      <c r="F37" s="189"/>
+      <c r="G37" s="189"/>
+      <c r="H37" s="189"/>
+      <c r="I37" s="189"/>
+      <c r="J37" s="189"/>
+      <c r="K37" s="189"/>
+      <c r="L37" s="189"/>
+      <c r="M37" s="189"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="D1:L1"/>
+  <mergeCells count="16">
+    <mergeCell ref="B32:M37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="D1:M1"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="E4:E5"/>
-    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="B32:L37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4385,142 +4487,142 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="189" t="s">
+    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B2" s="172" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="173">
+        <v>1</v>
+      </c>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="170"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B3" s="174" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="175" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="171"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B4" s="206" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="190">
+      <c r="C4" s="207"/>
+      <c r="D4" s="207"/>
+      <c r="E4" s="207"/>
+      <c r="F4" s="208"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="207"/>
+      <c r="E5" s="207"/>
+      <c r="F5" s="208"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="123"/>
+      <c r="B6" s="206"/>
+      <c r="C6" s="207"/>
+      <c r="D6" s="207"/>
+      <c r="E6" s="207"/>
+      <c r="F6" s="208"/>
+      <c r="N6" s="123"/>
+      <c r="O6" s="123"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="123"/>
+      <c r="B7" s="206"/>
+      <c r="C7" s="207"/>
+      <c r="D7" s="207"/>
+      <c r="E7" s="207"/>
+      <c r="F7" s="208"/>
+      <c r="N7" s="123"/>
+      <c r="O7" s="123"/>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="123"/>
+      <c r="B8" s="209"/>
+      <c r="C8" s="210"/>
+      <c r="D8" s="210"/>
+      <c r="E8" s="210"/>
+      <c r="F8" s="211"/>
+      <c r="N8" s="123"/>
+      <c r="O8" s="123"/>
+    </row>
+    <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="123"/>
+      <c r="N9" s="123"/>
+      <c r="O9" s="123"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="123"/>
+      <c r="B10" s="176" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="177">
         <v>1</v>
       </c>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="186"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="191" t="s">
+      <c r="D10" s="169"/>
+      <c r="E10" s="169"/>
+      <c r="F10" s="170"/>
+      <c r="N10" s="123"/>
+      <c r="O10" s="123"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="123"/>
+      <c r="B11" s="178" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="179" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="192" t="s">
+      <c r="F11" s="171"/>
+      <c r="N11" s="123"/>
+      <c r="O11" s="123"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B12" s="206" t="s">
         <v>111</v>
       </c>
-      <c r="F3" s="187"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="223" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="224"/>
-      <c r="D4" s="224"/>
-      <c r="E4" s="224"/>
-      <c r="F4" s="225"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="223"/>
-      <c r="C5" s="224"/>
-      <c r="D5" s="224"/>
-      <c r="E5" s="224"/>
-      <c r="F5" s="225"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="124"/>
-      <c r="B6" s="223"/>
-      <c r="C6" s="224"/>
-      <c r="D6" s="224"/>
-      <c r="E6" s="224"/>
-      <c r="F6" s="225"/>
-      <c r="N6" s="124"/>
-      <c r="O6" s="124"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="124"/>
-      <c r="B7" s="223"/>
-      <c r="C7" s="224"/>
-      <c r="D7" s="224"/>
-      <c r="E7" s="224"/>
-      <c r="F7" s="225"/>
-      <c r="N7" s="124"/>
-      <c r="O7" s="124"/>
-    </row>
-    <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="124"/>
-      <c r="B8" s="226"/>
-      <c r="C8" s="227"/>
-      <c r="D8" s="227"/>
-      <c r="E8" s="227"/>
-      <c r="F8" s="228"/>
-      <c r="N8" s="124"/>
-      <c r="O8" s="124"/>
-    </row>
-    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="124"/>
-      <c r="N9" s="124"/>
-      <c r="O9" s="124"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="124"/>
-      <c r="B10" s="194" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" s="195">
-        <v>1</v>
-      </c>
-      <c r="D10" s="185"/>
-      <c r="E10" s="185"/>
-      <c r="F10" s="186"/>
-      <c r="N10" s="124"/>
-      <c r="O10" s="124"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="124"/>
-      <c r="B11" s="196" t="s">
-        <v>110</v>
-      </c>
-      <c r="C11" s="197" t="s">
-        <v>113</v>
-      </c>
-      <c r="F11" s="187"/>
-      <c r="N11" s="124"/>
-      <c r="O11" s="124"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B12" s="223" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="224"/>
-      <c r="D12" s="224"/>
-      <c r="E12" s="224"/>
-      <c r="F12" s="225"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="223"/>
-      <c r="C13" s="224"/>
-      <c r="D13" s="224"/>
-      <c r="E13" s="224"/>
-      <c r="F13" s="225"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="223"/>
-      <c r="C14" s="224"/>
-      <c r="D14" s="224"/>
-      <c r="E14" s="224"/>
-      <c r="F14" s="225"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="223"/>
-      <c r="C15" s="224"/>
-      <c r="D15" s="224"/>
-      <c r="E15" s="224"/>
-      <c r="F15" s="225"/>
-    </row>
-    <row r="16" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="226"/>
-      <c r="C16" s="227"/>
-      <c r="D16" s="227"/>
-      <c r="E16" s="227"/>
-      <c r="F16" s="228"/>
+      <c r="C12" s="207"/>
+      <c r="D12" s="207"/>
+      <c r="E12" s="207"/>
+      <c r="F12" s="208"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B13" s="206"/>
+      <c r="C13" s="207"/>
+      <c r="D13" s="207"/>
+      <c r="E13" s="207"/>
+      <c r="F13" s="208"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B14" s="206"/>
+      <c r="C14" s="207"/>
+      <c r="D14" s="207"/>
+      <c r="E14" s="207"/>
+      <c r="F14" s="208"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B15" s="206"/>
+      <c r="C15" s="207"/>
+      <c r="D15" s="207"/>
+      <c r="E15" s="207"/>
+      <c r="F15" s="208"/>
+    </row>
+    <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="209"/>
+      <c r="C16" s="210"/>
+      <c r="D16" s="210"/>
+      <c r="E16" s="210"/>
+      <c r="F16" s="211"/>
     </row>
   </sheetData>
   <mergeCells count="2">
